--- a/compare/output/dscale_IndustryCO2_downscaled_SSP126.xlsx
+++ b/compare/output/dscale_IndustryCO2_downscaled_SSP126.xlsx
@@ -526,19 +526,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1719.833029</v>
+        <v>1402.692872</v>
       </c>
       <c r="F2" t="n">
-        <v>2684.866397</v>
+        <v>2334.537133</v>
       </c>
       <c r="G2" t="n">
-        <v>3751.488483</v>
+        <v>3393.441295</v>
       </c>
       <c r="H2" t="n">
-        <v>5167.221501</v>
+        <v>4822.470828</v>
       </c>
       <c r="I2" t="n">
-        <v>6867.651665</v>
+        <v>6613.781433</v>
       </c>
       <c r="J2" t="n">
         <v>8866.317846</v>
@@ -602,19 +602,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>166.450819</v>
+        <v>150.036386</v>
       </c>
       <c r="F3" t="n">
-        <v>228.369891</v>
+        <v>210.19027</v>
       </c>
       <c r="G3" t="n">
-        <v>297.198693</v>
+        <v>279.38026</v>
       </c>
       <c r="H3" t="n">
-        <v>389.508368</v>
+        <v>373.076136</v>
       </c>
       <c r="I3" t="n">
-        <v>495.283362</v>
+        <v>483.689903</v>
       </c>
       <c r="J3" t="n">
         <v>608.616336</v>
@@ -678,19 +678,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>383.176518</v>
+        <v>434.469366</v>
       </c>
       <c r="F4" t="n">
-        <v>384.052961</v>
+        <v>420.778219</v>
       </c>
       <c r="G4" t="n">
-        <v>433.108436</v>
+        <v>457.923787</v>
       </c>
       <c r="H4" t="n">
-        <v>524.000078</v>
+        <v>541.120849</v>
       </c>
       <c r="I4" t="n">
-        <v>629.49866</v>
+        <v>639.132567</v>
       </c>
       <c r="J4" t="n">
         <v>737.97229</v>
@@ -754,19 +754,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1113.364799</v>
+        <v>936.668889</v>
       </c>
       <c r="F5" t="n">
-        <v>1707.704748</v>
+        <v>1519.969002</v>
       </c>
       <c r="G5" t="n">
-        <v>2369.116114</v>
+        <v>2194.62599</v>
       </c>
       <c r="H5" t="n">
-        <v>3247.769166</v>
+        <v>3094.714039</v>
       </c>
       <c r="I5" t="n">
-        <v>4292.879936</v>
+        <v>4186.38935</v>
       </c>
       <c r="J5" t="n">
         <v>5488.378948</v>
@@ -830,19 +830,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>23526.6017</v>
+        <v>23360.667382</v>
       </c>
       <c r="F6" t="n">
-        <v>30585.967256</v>
+        <v>30432.28609</v>
       </c>
       <c r="G6" t="n">
-        <v>38836.337781</v>
+        <v>38398.524524</v>
       </c>
       <c r="H6" t="n">
-        <v>50395.203151</v>
+        <v>49691.71955</v>
       </c>
       <c r="I6" t="n">
-        <v>63957.472392</v>
+        <v>63307.537022</v>
       </c>
       <c r="J6" t="n">
         <v>78909.41957500001</v>
@@ -906,19 +906,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>15672.287067</v>
+        <v>17156.80442</v>
       </c>
       <c r="F7" t="n">
-        <v>18563.184053</v>
+        <v>20335.309484</v>
       </c>
       <c r="G7" t="n">
-        <v>22908.555141</v>
+        <v>25099.115869</v>
       </c>
       <c r="H7" t="n">
-        <v>28656.360312</v>
+        <v>31145.624233</v>
       </c>
       <c r="I7" t="n">
-        <v>34144.979305</v>
+        <v>36193.28092</v>
       </c>
       <c r="J7" t="n">
         <v>38077.335522</v>
@@ -982,19 +982,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4823.223963</v>
+        <v>4343.577831</v>
       </c>
       <c r="F8" t="n">
-        <v>6916.655733</v>
+        <v>6386.568227</v>
       </c>
       <c r="G8" t="n">
-        <v>9343.360360000001</v>
+        <v>8803.89738</v>
       </c>
       <c r="H8" t="n">
-        <v>12628.403346</v>
+        <v>12101.78606</v>
       </c>
       <c r="I8" t="n">
-        <v>16518.998248</v>
+        <v>16124.955954</v>
       </c>
       <c r="J8" t="n">
         <v>20912.627216</v>
@@ -1058,19 +1058,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>681.26124</v>
+        <v>815.4651679999999</v>
       </c>
       <c r="F9" t="n">
-        <v>593.23251</v>
+        <v>697.993126</v>
       </c>
       <c r="G9" t="n">
-        <v>589.876176</v>
+        <v>663.898252</v>
       </c>
       <c r="H9" t="n">
-        <v>646.448071</v>
+        <v>696.386717</v>
       </c>
       <c r="I9" t="n">
-        <v>719.769145</v>
+        <v>746.183536</v>
       </c>
       <c r="J9" t="n">
         <v>793.69025</v>
@@ -1134,19 +1134,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2193.779282</v>
+        <v>1857.673458</v>
       </c>
       <c r="F10" t="n">
-        <v>3303.512794</v>
+        <v>2923.978511</v>
       </c>
       <c r="G10" t="n">
-        <v>4559.500642</v>
+        <v>4158.311904</v>
       </c>
       <c r="H10" t="n">
-        <v>6282.103689</v>
+        <v>5884.957935</v>
       </c>
       <c r="I10" t="n">
-        <v>8409.803925</v>
+        <v>8110.470694</v>
       </c>
       <c r="J10" t="n">
         <v>10943.041709</v>
@@ -1210,19 +1210,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>13652.5685</v>
+        <v>14207.907245</v>
       </c>
       <c r="F11" t="n">
-        <v>16706.594715</v>
+        <v>17244.606891</v>
       </c>
       <c r="G11" t="n">
-        <v>20783.177649</v>
+        <v>21314.088113</v>
       </c>
       <c r="H11" t="n">
-        <v>26420.943995</v>
+        <v>26907.192265</v>
       </c>
       <c r="I11" t="n">
-        <v>32643.626304</v>
+        <v>32964.28862</v>
       </c>
       <c r="J11" t="n">
         <v>39033.375611</v>
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1848.266035</v>
+        <v>1526.924157</v>
       </c>
       <c r="F12" t="n">
-        <v>2729.941637</v>
+        <v>2393.835561</v>
       </c>
       <c r="G12" t="n">
-        <v>3657.533584</v>
+        <v>3332.248345</v>
       </c>
       <c r="H12" t="n">
-        <v>4879.487113</v>
+        <v>4580.491226</v>
       </c>
       <c r="I12" t="n">
-        <v>6292.323208</v>
+        <v>6080.87436</v>
       </c>
       <c r="J12" t="n">
         <v>7839.20155</v>
@@ -1362,19 +1362,19 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>8781.759647000001</v>
+        <v>8369.685425</v>
       </c>
       <c r="F13" t="n">
-        <v>12223.145271</v>
+        <v>11727.17545</v>
       </c>
       <c r="G13" t="n">
-        <v>16548.884357</v>
+        <v>15982.681698</v>
       </c>
       <c r="H13" t="n">
-        <v>22740.355347</v>
+        <v>22138.264298</v>
       </c>
       <c r="I13" t="n">
-        <v>30432.256258</v>
+        <v>29953.958048</v>
       </c>
       <c r="J13" t="n">
         <v>39413.828141</v>
@@ -1438,19 +1438,19 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>38676.999572</v>
+        <v>39767.746161</v>
       </c>
       <c r="F14" t="n">
-        <v>39328.589557</v>
+        <v>40582.132045</v>
       </c>
       <c r="G14" t="n">
-        <v>39898.061302</v>
+        <v>41114.267689</v>
       </c>
       <c r="H14" t="n">
-        <v>41654.422157</v>
+        <v>42757.550473</v>
       </c>
       <c r="I14" t="n">
-        <v>42820.27562</v>
+        <v>43602.982206</v>
       </c>
       <c r="J14" t="n">
         <v>43191.512646</v>
@@ -1514,19 +1514,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>61315.394961</v>
+        <v>60866.759748</v>
       </c>
       <c r="F15" t="n">
-        <v>72552.47672000001</v>
+        <v>72232.916637</v>
       </c>
       <c r="G15" t="n">
-        <v>79835.308187</v>
+        <v>79681.908193</v>
       </c>
       <c r="H15" t="n">
-        <v>88490.74277500001</v>
+        <v>88428.58807899999</v>
       </c>
       <c r="I15" t="n">
-        <v>96617.952462</v>
+        <v>96588.11865</v>
       </c>
       <c r="J15" t="n">
         <v>105148.279778</v>
@@ -1590,19 +1590,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>8367.880422</v>
+        <v>8785.304991000001</v>
       </c>
       <c r="F16" t="n">
-        <v>7245.70573</v>
+        <v>7613.976301</v>
       </c>
       <c r="G16" t="n">
-        <v>6647.304118</v>
+        <v>6866.851402</v>
       </c>
       <c r="H16" t="n">
-        <v>6766.820081</v>
+        <v>6878.582756</v>
       </c>
       <c r="I16" t="n">
-        <v>7140.245236</v>
+        <v>7181.639284</v>
       </c>
       <c r="J16" t="n">
         <v>7701.569887</v>
@@ -1666,19 +1666,19 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>16165.269332</v>
+        <v>15083.954834</v>
       </c>
       <c r="F17" t="n">
-        <v>21284.38686</v>
+        <v>19932.194777</v>
       </c>
       <c r="G17" t="n">
-        <v>24764.433143</v>
+        <v>23461.911026</v>
       </c>
       <c r="H17" t="n">
-        <v>28471.842369</v>
+        <v>27330.991598</v>
       </c>
       <c r="I17" t="n">
-        <v>32178.222728</v>
+        <v>31403.815249</v>
       </c>
       <c r="J17" t="n">
         <v>36620.363168</v>
@@ -1742,19 +1742,19 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>8122.938468</v>
+        <v>8144.717021</v>
       </c>
       <c r="F18" t="n">
-        <v>9041.660209</v>
+        <v>9091.599316</v>
       </c>
       <c r="G18" t="n">
-        <v>9414.47761</v>
+        <v>9434.646049999999</v>
       </c>
       <c r="H18" t="n">
-        <v>10073.136001</v>
+        <v>10061.250477</v>
       </c>
       <c r="I18" t="n">
-        <v>10753.369295</v>
+        <v>10733.509952</v>
       </c>
       <c r="J18" t="n">
         <v>11491.244446</v>
@@ -1818,19 +1818,19 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>14069.296489</v>
+        <v>16121.842387</v>
       </c>
       <c r="F19" t="n">
-        <v>15423.678395</v>
+        <v>18442.368198</v>
       </c>
       <c r="G19" t="n">
-        <v>17270.560758</v>
+        <v>20874.087336</v>
       </c>
       <c r="H19" t="n">
-        <v>19254.550858</v>
+        <v>23044.025372</v>
       </c>
       <c r="I19" t="n">
-        <v>20999.923256</v>
+        <v>24146.445601</v>
       </c>
       <c r="J19" t="n">
         <v>21147.65146</v>
@@ -1894,19 +1894,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>921.614407</v>
+        <v>1017.179784</v>
       </c>
       <c r="F20" t="n">
-        <v>988.754293</v>
+        <v>1114.693817</v>
       </c>
       <c r="G20" t="n">
-        <v>1126.445347</v>
+        <v>1281.278365</v>
       </c>
       <c r="H20" t="n">
-        <v>1268.106307</v>
+        <v>1433.51598</v>
       </c>
       <c r="I20" t="n">
-        <v>1396.741354</v>
+        <v>1529.010583</v>
       </c>
       <c r="J20" t="n">
         <v>1479.886828</v>
@@ -1970,19 +1970,19 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>332.971896</v>
+        <v>265.984668</v>
       </c>
       <c r="F21" t="n">
-        <v>505.729121</v>
+        <v>409.438813</v>
       </c>
       <c r="G21" t="n">
-        <v>697.141245</v>
+        <v>584.253937</v>
       </c>
       <c r="H21" t="n">
-        <v>928.047915</v>
+        <v>811.601664</v>
       </c>
       <c r="I21" t="n">
-        <v>1231.988639</v>
+        <v>1137.303589</v>
       </c>
       <c r="J21" t="n">
         <v>1645.447839</v>
@@ -2046,19 +2046,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4990.759095</v>
+        <v>4499.588559</v>
       </c>
       <c r="F22" t="n">
-        <v>7286.27689</v>
+        <v>6609.125462</v>
       </c>
       <c r="G22" t="n">
-        <v>9918.131857</v>
+        <v>9121.825704000001</v>
       </c>
       <c r="H22" t="n">
-        <v>13139.537393</v>
+        <v>12284.372643</v>
       </c>
       <c r="I22" t="n">
-        <v>17395.05689</v>
+        <v>16661.698382</v>
       </c>
       <c r="J22" t="n">
         <v>23036.391828</v>
@@ -2122,19 +2122,19 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3589.823645</v>
+        <v>3311.937232</v>
       </c>
       <c r="F23" t="n">
-        <v>5351.701782</v>
+        <v>4948.794032</v>
       </c>
       <c r="G23" t="n">
-        <v>7545.19246</v>
+        <v>7070.85956</v>
       </c>
       <c r="H23" t="n">
-        <v>10367.457963</v>
+        <v>9878.840332</v>
       </c>
       <c r="I23" t="n">
-        <v>14159.379369</v>
+        <v>13757.792949</v>
       </c>
       <c r="J23" t="n">
         <v>19159.660433</v>
@@ -2198,19 +2198,19 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>800.59491</v>
+        <v>842.544636</v>
       </c>
       <c r="F24" t="n">
-        <v>933.68681</v>
+        <v>986.118342</v>
       </c>
       <c r="G24" t="n">
-        <v>1119.137279</v>
+        <v>1180.206379</v>
       </c>
       <c r="H24" t="n">
-        <v>1338.248781</v>
+        <v>1401.662318</v>
       </c>
       <c r="I24" t="n">
-        <v>1594.765857</v>
+        <v>1644.150232</v>
       </c>
       <c r="J24" t="n">
         <v>1875.74104</v>
@@ -2274,19 +2274,19 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>332.716976</v>
+        <v>334.429797</v>
       </c>
       <c r="F25" t="n">
-        <v>398.962102</v>
+        <v>394.984297</v>
       </c>
       <c r="G25" t="n">
-        <v>492.462964</v>
+        <v>486.307224</v>
       </c>
       <c r="H25" t="n">
-        <v>608.912791</v>
+        <v>604.199721</v>
       </c>
       <c r="I25" t="n">
-        <v>751.069074</v>
+        <v>748.1238499999999</v>
       </c>
       <c r="J25" t="n">
         <v>920.0100619999999</v>
@@ -2350,19 +2350,19 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>8454.732576</v>
+        <v>7205.230912</v>
       </c>
       <c r="F26" t="n">
-        <v>13168.419508</v>
+        <v>11313.791754</v>
       </c>
       <c r="G26" t="n">
-        <v>18726.194638</v>
+        <v>16371.694851</v>
       </c>
       <c r="H26" t="n">
-        <v>25915.100209</v>
+        <v>23230.342963</v>
       </c>
       <c r="I26" t="n">
-        <v>35988.908104</v>
+        <v>33578.067938</v>
       </c>
       <c r="J26" t="n">
         <v>50283.621222</v>
@@ -2426,19 +2426,19 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3761.041728</v>
+        <v>3730.456695</v>
       </c>
       <c r="F27" t="n">
-        <v>5015.665315</v>
+        <v>4963.809095</v>
       </c>
       <c r="G27" t="n">
-        <v>6531.903217</v>
+        <v>6435.027853</v>
       </c>
       <c r="H27" t="n">
-        <v>8489.144951</v>
+        <v>8354.903753000001</v>
       </c>
       <c r="I27" t="n">
-        <v>11105.114107</v>
+        <v>10967.444043</v>
       </c>
       <c r="J27" t="n">
         <v>14482.995617</v>
@@ -2502,19 +2502,19 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3479.852115</v>
+        <v>3404.209168</v>
       </c>
       <c r="F28" t="n">
-        <v>4299.583941</v>
+        <v>4189.334348</v>
       </c>
       <c r="G28" t="n">
-        <v>5475.016001</v>
+        <v>5496.644558</v>
       </c>
       <c r="H28" t="n">
-        <v>6806.207692</v>
+        <v>7071.850115</v>
       </c>
       <c r="I28" t="n">
-        <v>8093.136735</v>
+        <v>8546.04622</v>
       </c>
       <c r="J28" t="n">
         <v>8710.713221</v>
@@ -2578,19 +2578,19 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2513.352058</v>
+        <v>2231.275117</v>
       </c>
       <c r="F29" t="n">
-        <v>3759.369438</v>
+        <v>3316.797765</v>
       </c>
       <c r="G29" t="n">
-        <v>5553.265616</v>
+        <v>4985.400121</v>
       </c>
       <c r="H29" t="n">
-        <v>8017.798787</v>
+        <v>7373.697928</v>
       </c>
       <c r="I29" t="n">
-        <v>11066.093087</v>
+        <v>10521.439787</v>
       </c>
       <c r="J29" t="n">
         <v>14706.678661</v>
@@ -2654,19 +2654,19 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4026.769462</v>
+        <v>3298.527512</v>
       </c>
       <c r="F30" t="n">
-        <v>6416.192619</v>
+        <v>5308.830533</v>
       </c>
       <c r="G30" t="n">
-        <v>9778.376592000001</v>
+        <v>8349.295585</v>
       </c>
       <c r="H30" t="n">
-        <v>14482.479425</v>
+        <v>12855.118498</v>
       </c>
       <c r="I30" t="n">
-        <v>20495.424406</v>
+        <v>19105.093098</v>
       </c>
       <c r="J30" t="n">
         <v>27969.722363</v>
@@ -2730,19 +2730,19 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>806.693372</v>
+        <v>552.010762</v>
       </c>
       <c r="F31" t="n">
-        <v>1411.904042</v>
+        <v>1061.967651</v>
       </c>
       <c r="G31" t="n">
-        <v>2179.117359</v>
+        <v>1756.897833</v>
       </c>
       <c r="H31" t="n">
-        <v>3203.171571</v>
+        <v>2745.967829</v>
       </c>
       <c r="I31" t="n">
-        <v>4468.82079</v>
+        <v>4095.996355</v>
       </c>
       <c r="J31" t="n">
         <v>6010.133732</v>
@@ -2806,19 +2806,19 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6289.101194</v>
+        <v>5992.371127</v>
       </c>
       <c r="F32" t="n">
-        <v>8218.608969999999</v>
+        <v>7662.487187</v>
       </c>
       <c r="G32" t="n">
-        <v>11147.598628</v>
+        <v>10401.593272</v>
       </c>
       <c r="H32" t="n">
-        <v>15096.572394</v>
+        <v>14275.223752</v>
       </c>
       <c r="I32" t="n">
-        <v>19667.059462</v>
+        <v>19022.853054</v>
       </c>
       <c r="J32" t="n">
         <v>24622.751608</v>
@@ -2882,19 +2882,19 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6715.921079</v>
+        <v>6545.733519</v>
       </c>
       <c r="F33" t="n">
-        <v>8862.687172</v>
+        <v>8527.666638000001</v>
       </c>
       <c r="G33" t="n">
-        <v>12106.224039</v>
+        <v>11684.986552</v>
       </c>
       <c r="H33" t="n">
-        <v>16421.574212</v>
+        <v>15974.821319</v>
       </c>
       <c r="I33" t="n">
-        <v>21339.534446</v>
+        <v>20987.182454</v>
       </c>
       <c r="J33" t="n">
         <v>26610.765769</v>
@@ -2958,19 +2958,19 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>12946.422161</v>
+        <v>8923.015926</v>
       </c>
       <c r="F34" t="n">
-        <v>23581.852181</v>
+        <v>18061.090885</v>
       </c>
       <c r="G34" t="n">
-        <v>37633.050705</v>
+        <v>31154.218558</v>
       </c>
       <c r="H34" t="n">
-        <v>56692.60326</v>
+        <v>49916.522479</v>
       </c>
       <c r="I34" t="n">
-        <v>80317.61112</v>
+        <v>74925.21144100001</v>
       </c>
       <c r="J34" t="n">
         <v>108867.741395</v>
@@ -3034,19 +3034,19 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3455.694578</v>
+        <v>4029.948938</v>
       </c>
       <c r="F35" t="n">
-        <v>4111.545509</v>
+        <v>5056.362058</v>
       </c>
       <c r="G35" t="n">
-        <v>5239.149887</v>
+        <v>6657.364049</v>
       </c>
       <c r="H35" t="n">
-        <v>6281.008711</v>
+        <v>8018.799348</v>
       </c>
       <c r="I35" t="n">
-        <v>6649.732499</v>
+        <v>8117.393129</v>
       </c>
       <c r="J35" t="n">
         <v>5982.729306</v>
@@ -3110,19 +3110,19 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>202.237667</v>
+        <v>211.831523</v>
       </c>
       <c r="F36" t="n">
-        <v>235.791872</v>
+        <v>246.928786</v>
       </c>
       <c r="G36" t="n">
-        <v>282.440989</v>
+        <v>290.586355</v>
       </c>
       <c r="H36" t="n">
-        <v>344.18038</v>
+        <v>347.455395</v>
       </c>
       <c r="I36" t="n">
-        <v>411.309097</v>
+        <v>410.466195</v>
       </c>
       <c r="J36" t="n">
         <v>480.730639</v>
@@ -3186,19 +3186,19 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4731.451886</v>
+        <v>5980.27172</v>
       </c>
       <c r="F37" t="n">
-        <v>3749.022919</v>
+        <v>5139.725799</v>
       </c>
       <c r="G37" t="n">
-        <v>3421.364417</v>
+        <v>4852.167596</v>
       </c>
       <c r="H37" t="n">
-        <v>3225.984912</v>
+        <v>4593.162912</v>
       </c>
       <c r="I37" t="n">
-        <v>2784.879294</v>
+        <v>3788.10014</v>
       </c>
       <c r="J37" t="n">
         <v>1862.147765</v>
@@ -3262,19 +3262,19 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>7863.116714</v>
+        <v>7454.735798</v>
       </c>
       <c r="F38" t="n">
-        <v>10797.820508</v>
+        <v>10137.826157</v>
       </c>
       <c r="G38" t="n">
-        <v>14995.805237</v>
+        <v>14137.254169</v>
       </c>
       <c r="H38" t="n">
-        <v>20704.115296</v>
+        <v>19766.836363</v>
       </c>
       <c r="I38" t="n">
-        <v>27438.002511</v>
+        <v>26697.703088</v>
       </c>
       <c r="J38" t="n">
         <v>34889.653934</v>
@@ -3338,19 +3338,19 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2453.866137</v>
+        <v>2072.185271</v>
       </c>
       <c r="F39" t="n">
-        <v>3656.829801</v>
+        <v>3111.042416</v>
       </c>
       <c r="G39" t="n">
-        <v>5267.4674</v>
+        <v>4616.178674</v>
       </c>
       <c r="H39" t="n">
-        <v>7377.816859</v>
+        <v>6694.726893</v>
       </c>
       <c r="I39" t="n">
-        <v>9839.776574</v>
+        <v>9308.528274</v>
       </c>
       <c r="J39" t="n">
         <v>12584.259464</v>
@@ -3414,19 +3414,19 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>319.719078</v>
+        <v>245.835203</v>
       </c>
       <c r="F40" t="n">
-        <v>518.279101</v>
+        <v>415.933024</v>
       </c>
       <c r="G40" t="n">
-        <v>773.741252</v>
+        <v>650.760207</v>
       </c>
       <c r="H40" t="n">
-        <v>1111.71082</v>
+        <v>979.06037</v>
       </c>
       <c r="I40" t="n">
-        <v>1523.542631</v>
+        <v>1415.898998</v>
       </c>
       <c r="J40" t="n">
         <v>2014.828462</v>
@@ -3490,19 +3490,19 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>384.08891</v>
+        <v>302.735426</v>
       </c>
       <c r="F41" t="n">
-        <v>629.220728</v>
+        <v>516.416028</v>
       </c>
       <c r="G41" t="n">
-        <v>945.528845</v>
+        <v>808.149152</v>
       </c>
       <c r="H41" t="n">
-        <v>1367.858646</v>
+        <v>1217.542952</v>
       </c>
       <c r="I41" t="n">
-        <v>1885.258617</v>
+        <v>1760.576163</v>
       </c>
       <c r="J41" t="n">
         <v>2506.718002</v>
@@ -3566,19 +3566,19 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4365.833469</v>
+        <v>5588.29063</v>
       </c>
       <c r="F42" t="n">
-        <v>3492.674482</v>
+        <v>4925.555787</v>
       </c>
       <c r="G42" t="n">
-        <v>3038.941655</v>
+        <v>4506.196867</v>
       </c>
       <c r="H42" t="n">
-        <v>2663.28609</v>
+        <v>4032.583986</v>
       </c>
       <c r="I42" t="n">
-        <v>2086.679328</v>
+        <v>3081.034818</v>
       </c>
       <c r="J42" t="n">
         <v>1060.709262</v>
@@ -3642,19 +3642,19 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1066.635382</v>
+        <v>881.262859</v>
       </c>
       <c r="F43" t="n">
-        <v>1834.243842</v>
+        <v>1584.604038</v>
       </c>
       <c r="G43" t="n">
-        <v>2883.491059</v>
+        <v>2596.928231</v>
       </c>
       <c r="H43" t="n">
-        <v>4301.694882</v>
+        <v>4002.924681</v>
       </c>
       <c r="I43" t="n">
-        <v>6037.791794</v>
+        <v>5800.191809</v>
       </c>
       <c r="J43" t="n">
         <v>8068.223059</v>
@@ -3718,19 +3718,19 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3513.281391</v>
+        <v>2768.148462</v>
       </c>
       <c r="F44" t="n">
-        <v>5878.864797</v>
+        <v>4817.075749</v>
       </c>
       <c r="G44" t="n">
-        <v>9069.19893</v>
+        <v>7745.00985</v>
       </c>
       <c r="H44" t="n">
-        <v>13462.22324</v>
+        <v>11995.476722</v>
       </c>
       <c r="I44" t="n">
-        <v>18993.22656</v>
+        <v>17778.744254</v>
       </c>
       <c r="J44" t="n">
         <v>25692.806298</v>
@@ -3794,19 +3794,19 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1369.777687</v>
+        <v>1388.588359</v>
       </c>
       <c r="F45" t="n">
-        <v>1756.935121</v>
+        <v>1767.809728</v>
       </c>
       <c r="G45" t="n">
-        <v>2334.850298</v>
+        <v>2339.985004</v>
       </c>
       <c r="H45" t="n">
-        <v>3098.63586</v>
+        <v>3098.644075</v>
       </c>
       <c r="I45" t="n">
-        <v>3946.647721</v>
+        <v>3940.25119</v>
       </c>
       <c r="J45" t="n">
         <v>4827.92376</v>
@@ -3870,19 +3870,19 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3290.71304</v>
+        <v>2381.528199</v>
       </c>
       <c r="F46" t="n">
-        <v>5971.060615</v>
+        <v>4637.172418</v>
       </c>
       <c r="G46" t="n">
-        <v>9694.173580000001</v>
+        <v>7990.217848</v>
       </c>
       <c r="H46" t="n">
-        <v>15030.021272</v>
+        <v>13072.444638</v>
       </c>
       <c r="I46" t="n">
-        <v>22164.662953</v>
+        <v>20467.101536</v>
       </c>
       <c r="J46" t="n">
         <v>31436.227683</v>
@@ -3946,19 +3946,19 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>80548.62530299999</v>
+        <v>86712.762271</v>
       </c>
       <c r="F47" t="n">
-        <v>102378.85324</v>
+        <v>112087.132651</v>
       </c>
       <c r="G47" t="n">
-        <v>133792.039907</v>
+        <v>146076.481505</v>
       </c>
       <c r="H47" t="n">
-        <v>175226.739794</v>
+        <v>188865.044641</v>
       </c>
       <c r="I47" t="n">
-        <v>220289.046994</v>
+        <v>231678.841169</v>
       </c>
       <c r="J47" t="n">
         <v>262728.863189</v>
@@ -4022,19 +4022,19 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5576.41297</v>
+        <v>5830.963073</v>
       </c>
       <c r="F48" t="n">
-        <v>6919.122064</v>
+        <v>7223.025646</v>
       </c>
       <c r="G48" t="n">
-        <v>9021.079126000001</v>
+        <v>9384.744998</v>
       </c>
       <c r="H48" t="n">
-        <v>11708.544509</v>
+        <v>12072.715709</v>
       </c>
       <c r="I48" t="n">
-        <v>14594.92893</v>
+        <v>14860.263761</v>
       </c>
       <c r="J48" t="n">
         <v>17413.617226</v>
@@ -4098,19 +4098,19 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1299.735115</v>
+        <v>1017.796685</v>
       </c>
       <c r="F49" t="n">
-        <v>2139.136339</v>
+        <v>1744.85708</v>
       </c>
       <c r="G49" t="n">
-        <v>3243.861346</v>
+        <v>2761.025166</v>
       </c>
       <c r="H49" t="n">
-        <v>4739.265082</v>
+        <v>4205.957407</v>
       </c>
       <c r="I49" t="n">
-        <v>6600.98374</v>
+        <v>6156.545297</v>
       </c>
       <c r="J49" t="n">
         <v>8867.169656</v>
@@ -4174,19 +4174,19 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>49.360415</v>
+        <v>46.454333</v>
       </c>
       <c r="F50" t="n">
-        <v>65.202961</v>
+        <v>60.842165</v>
       </c>
       <c r="G50" t="n">
-        <v>85.88878099999999</v>
+        <v>80.004784</v>
       </c>
       <c r="H50" t="n">
-        <v>112.614546</v>
+        <v>105.608106</v>
       </c>
       <c r="I50" t="n">
-        <v>142.828648</v>
+        <v>136.785494</v>
       </c>
       <c r="J50" t="n">
         <v>175.804751</v>
@@ -4250,19 +4250,19 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2764.327007</v>
+        <v>2296.892495</v>
       </c>
       <c r="F51" t="n">
-        <v>4369.041687</v>
+        <v>3660.392602</v>
       </c>
       <c r="G51" t="n">
-        <v>6629.615703</v>
+        <v>5710.704539</v>
       </c>
       <c r="H51" t="n">
-        <v>9775.108416999999</v>
+        <v>8717.278713</v>
       </c>
       <c r="I51" t="n">
-        <v>13773.089522</v>
+        <v>12866.943555</v>
       </c>
       <c r="J51" t="n">
         <v>18691.643736</v>
@@ -4326,19 +4326,19 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1627.492424</v>
+        <v>1427.463295</v>
       </c>
       <c r="F52" t="n">
-        <v>2359.243934</v>
+        <v>2041.961152</v>
       </c>
       <c r="G52" t="n">
-        <v>3394.464601</v>
+        <v>2974.58504</v>
       </c>
       <c r="H52" t="n">
-        <v>4819.47432</v>
+        <v>4336.868569</v>
       </c>
       <c r="I52" t="n">
-        <v>6577.365289</v>
+        <v>6171.150956</v>
       </c>
       <c r="J52" t="n">
         <v>8673.7672</v>
@@ -4478,19 +4478,19 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>76144.027775</v>
+        <v>76284.873498</v>
       </c>
       <c r="F54" t="n">
-        <v>80714.848855</v>
+        <v>80804.251349</v>
       </c>
       <c r="G54" t="n">
-        <v>87320.23906199999</v>
+        <v>87384.00992700001</v>
       </c>
       <c r="H54" t="n">
-        <v>90085.53058200001</v>
+        <v>90125.783629</v>
       </c>
       <c r="I54" t="n">
-        <v>95900.685631</v>
+        <v>95920.593719</v>
       </c>
       <c r="J54" t="n">
         <v>105807.375772</v>
@@ -4554,19 +4554,19 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>17346.055723</v>
+        <v>17205.209999</v>
       </c>
       <c r="F55" t="n">
-        <v>18877.49445</v>
+        <v>18788.091956</v>
       </c>
       <c r="G55" t="n">
-        <v>20517.379091</v>
+        <v>20453.608227</v>
       </c>
       <c r="H55" t="n">
-        <v>21063.897243</v>
+        <v>21023.644196</v>
       </c>
       <c r="I55" t="n">
-        <v>22179.021458</v>
+        <v>22159.113371</v>
       </c>
       <c r="J55" t="n">
         <v>24079.584195</v>
@@ -4782,19 +4782,19 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>158.299895</v>
+        <v>143.763061</v>
       </c>
       <c r="F58" t="n">
-        <v>224.531003</v>
+        <v>208.643966</v>
       </c>
       <c r="G58" t="n">
-        <v>284.777094</v>
+        <v>271.270112</v>
       </c>
       <c r="H58" t="n">
-        <v>336.310254</v>
+        <v>326.262618</v>
       </c>
       <c r="I58" t="n">
-        <v>387.064773</v>
+        <v>381.272673</v>
       </c>
       <c r="J58" t="n">
         <v>446.755479</v>
@@ -4858,19 +4858,19 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>133.769787</v>
+        <v>113.164905</v>
       </c>
       <c r="F59" t="n">
-        <v>214.831412</v>
+        <v>192.177468</v>
       </c>
       <c r="G59" t="n">
-        <v>282.966085</v>
+        <v>263.511702</v>
       </c>
       <c r="H59" t="n">
-        <v>339.435075</v>
+        <v>324.962122</v>
       </c>
       <c r="I59" t="n">
-        <v>393.523223</v>
+        <v>385.275631</v>
       </c>
       <c r="J59" t="n">
         <v>455.757849</v>
@@ -4934,19 +4934,19 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>160.837532</v>
+        <v>154.129064</v>
       </c>
       <c r="F60" t="n">
-        <v>190.565845</v>
+        <v>181.944093</v>
       </c>
       <c r="G60" t="n">
-        <v>223.507148</v>
+        <v>215.413474</v>
       </c>
       <c r="H60" t="n">
-        <v>251.695583</v>
+        <v>245.469102</v>
       </c>
       <c r="I60" t="n">
-        <v>277.443146</v>
+        <v>273.92225</v>
       </c>
       <c r="J60" t="n">
         <v>306.195017</v>
@@ -5010,19 +5010,19 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>3008.03062</v>
+        <v>2864.584294</v>
       </c>
       <c r="F61" t="n">
-        <v>3891.686041</v>
+        <v>3747.105373</v>
       </c>
       <c r="G61" t="n">
-        <v>4716.55991</v>
+        <v>4600.063146</v>
       </c>
       <c r="H61" t="n">
-        <v>5427.544221</v>
+        <v>5340.917674</v>
       </c>
       <c r="I61" t="n">
-        <v>6135.842342</v>
+        <v>6084.507789</v>
       </c>
       <c r="J61" t="n">
         <v>6972.915389</v>
@@ -5086,19 +5086,19 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>9881.838471999999</v>
+        <v>10001.694724</v>
       </c>
       <c r="F62" t="n">
-        <v>10641.529705</v>
+        <v>10930.004686</v>
       </c>
       <c r="G62" t="n">
-        <v>11071.992006</v>
+        <v>11426.680748</v>
       </c>
       <c r="H62" t="n">
-        <v>11081.760182</v>
+        <v>11377.532699</v>
       </c>
       <c r="I62" t="n">
-        <v>10958.613192</v>
+        <v>11125.546136</v>
       </c>
       <c r="J62" t="n">
         <v>10939.177631</v>
@@ -5162,19 +5162,19 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>7497.36326</v>
+        <v>7345.314882</v>
       </c>
       <c r="F63" t="n">
-        <v>9028.452375999999</v>
+        <v>8928.147869</v>
       </c>
       <c r="G63" t="n">
-        <v>10386.169226</v>
+        <v>10341.696202</v>
       </c>
       <c r="H63" t="n">
-        <v>11457.034842</v>
+        <v>11442.910558</v>
       </c>
       <c r="I63" t="n">
-        <v>12430.069851</v>
+        <v>12428.696523</v>
       </c>
       <c r="J63" t="n">
         <v>13543.161328</v>
@@ -5238,19 +5238,19 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>42.049536</v>
+        <v>36.040388</v>
       </c>
       <c r="F64" t="n">
-        <v>63.093578</v>
+        <v>56.687921</v>
       </c>
       <c r="G64" t="n">
-        <v>79.588499</v>
+        <v>74.24069799999999</v>
       </c>
       <c r="H64" t="n">
-        <v>92.065622</v>
+        <v>88.207582</v>
       </c>
       <c r="I64" t="n">
-        <v>103.327426</v>
+        <v>101.197951</v>
       </c>
       <c r="J64" t="n">
         <v>116.224944</v>
@@ -5314,19 +5314,19 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>8672.038280999999</v>
+        <v>7970.21277</v>
       </c>
       <c r="F65" t="n">
-        <v>12315.714209</v>
+        <v>11600.338123</v>
       </c>
       <c r="G65" t="n">
-        <v>15578.509268</v>
+        <v>15013.492696</v>
       </c>
       <c r="H65" t="n">
-        <v>18317.690777</v>
+        <v>17921.911401</v>
       </c>
       <c r="I65" t="n">
-        <v>20923.473515</v>
+        <v>20706.36769</v>
       </c>
       <c r="J65" t="n">
         <v>23869.261529</v>
@@ -5390,19 +5390,19 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5280.877455</v>
+        <v>4948.203837</v>
       </c>
       <c r="F66" t="n">
-        <v>7167.627886</v>
+        <v>6850.694983</v>
       </c>
       <c r="G66" t="n">
-        <v>8820.307522999999</v>
+        <v>8597.068879</v>
       </c>
       <c r="H66" t="n">
-        <v>10126.094687</v>
+        <v>9989.897005999999</v>
       </c>
       <c r="I66" t="n">
-        <v>11297.315501</v>
+        <v>11233.199957</v>
       </c>
       <c r="J66" t="n">
         <v>12577.862169</v>
@@ -5466,19 +5466,19 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5526.914351</v>
+        <v>4748.818204</v>
       </c>
       <c r="F67" t="n">
-        <v>8498.517184</v>
+        <v>7676.746004</v>
       </c>
       <c r="G67" t="n">
-        <v>10912.991803</v>
+        <v>10239.252787</v>
       </c>
       <c r="H67" t="n">
-        <v>12781.802813</v>
+        <v>12308.410895</v>
       </c>
       <c r="I67" t="n">
-        <v>14464.036967</v>
+        <v>14210.560847</v>
       </c>
       <c r="J67" t="n">
         <v>16328.444114</v>
@@ -5542,19 +5542,19 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2834.398189</v>
+        <v>2900.815324</v>
       </c>
       <c r="F68" t="n">
-        <v>3046.669408</v>
+        <v>3172.021861</v>
       </c>
       <c r="G68" t="n">
-        <v>3248.209326</v>
+        <v>3425.815026</v>
       </c>
       <c r="H68" t="n">
-        <v>3251.475078</v>
+        <v>3425.094738</v>
       </c>
       <c r="I68" t="n">
-        <v>3121.465274</v>
+        <v>3232.358264</v>
       </c>
       <c r="J68" t="n">
         <v>2955.37781</v>
@@ -5618,19 +5618,19 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>70.53183799999999</v>
+        <v>60.275394</v>
       </c>
       <c r="F69" t="n">
-        <v>109.361689</v>
+        <v>98.248198</v>
       </c>
       <c r="G69" t="n">
-        <v>142.222534</v>
+        <v>132.686595</v>
       </c>
       <c r="H69" t="n">
-        <v>169.479891</v>
+        <v>162.381924</v>
       </c>
       <c r="I69" t="n">
-        <v>195.604448</v>
+        <v>191.559704</v>
       </c>
       <c r="J69" t="n">
         <v>224.953725</v>
@@ -5694,19 +5694,19 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3391.458158</v>
+        <v>3017.844764</v>
       </c>
       <c r="F70" t="n">
-        <v>4891.441384</v>
+        <v>4504.908475</v>
       </c>
       <c r="G70" t="n">
-        <v>6102.177926</v>
+        <v>5793.503656</v>
       </c>
       <c r="H70" t="n">
-        <v>7002.527788</v>
+        <v>6790.659828</v>
       </c>
       <c r="I70" t="n">
-        <v>7766.196856</v>
+        <v>7655.642915</v>
       </c>
       <c r="J70" t="n">
         <v>8580.247874000001</v>
@@ -5770,19 +5770,19 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3548.492019</v>
+        <v>3614.721098</v>
       </c>
       <c r="F71" t="n">
-        <v>4009.643869</v>
+        <v>4143.267107</v>
       </c>
       <c r="G71" t="n">
-        <v>4363.283644</v>
+        <v>4511.217536</v>
       </c>
       <c r="H71" t="n">
-        <v>4612.006969</v>
+        <v>4726.948073</v>
       </c>
       <c r="I71" t="n">
-        <v>4861.865202</v>
+        <v>4926.001096</v>
       </c>
       <c r="J71" t="n">
         <v>5181.735332</v>
@@ -5846,19 +5846,19 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3398.605556</v>
+        <v>3105.590498</v>
       </c>
       <c r="F72" t="n">
-        <v>4540.945546</v>
+        <v>4240.401895</v>
       </c>
       <c r="G72" t="n">
-        <v>5437.875518</v>
+        <v>5200.044529</v>
       </c>
       <c r="H72" t="n">
-        <v>6058.623104</v>
+        <v>5895.867567</v>
       </c>
       <c r="I72" t="n">
-        <v>6566.495409</v>
+        <v>6481.154336</v>
       </c>
       <c r="J72" t="n">
         <v>7109.264186</v>
@@ -5922,19 +5922,19 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>20070.986571</v>
+        <v>22657.85053</v>
       </c>
       <c r="F73" t="n">
-        <v>11712.312487</v>
+        <v>14022.119427</v>
       </c>
       <c r="G73" t="n">
-        <v>6856.920959</v>
+        <v>8407.403757</v>
       </c>
       <c r="H73" t="n">
-        <v>4283.6692</v>
+        <v>5225.576823</v>
       </c>
       <c r="I73" t="n">
-        <v>2702.786522</v>
+        <v>3169.954278</v>
       </c>
       <c r="J73" t="n">
         <v>1438.062871</v>
@@ -5998,19 +5998,19 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>43.49066</v>
+        <v>36.958445</v>
       </c>
       <c r="F74" t="n">
-        <v>64.479739</v>
+        <v>57.945914</v>
       </c>
       <c r="G74" t="n">
-        <v>80.31196799999999</v>
+        <v>75.008895</v>
       </c>
       <c r="H74" t="n">
-        <v>92.30651899999999</v>
+        <v>88.511995</v>
       </c>
       <c r="I74" t="n">
-        <v>103.188199</v>
+        <v>101.093805</v>
       </c>
       <c r="J74" t="n">
         <v>115.555192</v>
@@ -6074,19 +6074,19 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4766.195821</v>
+        <v>4520.846829</v>
       </c>
       <c r="F75" t="n">
-        <v>5301.033647</v>
+        <v>5083.867791</v>
       </c>
       <c r="G75" t="n">
-        <v>5782.124322</v>
+        <v>5578.891119</v>
       </c>
       <c r="H75" t="n">
-        <v>5836.313003</v>
+        <v>5682.153722</v>
       </c>
       <c r="I75" t="n">
-        <v>5693.567857</v>
+        <v>5613.844245</v>
       </c>
       <c r="J75" t="n">
         <v>5545.317978</v>
@@ -6150,19 +6150,19 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>11992.303205</v>
+        <v>11904.095742</v>
       </c>
       <c r="F76" t="n">
-        <v>13815.337061</v>
+        <v>13698.743699</v>
       </c>
       <c r="G76" t="n">
-        <v>16896.820828</v>
+        <v>16591.738463</v>
       </c>
       <c r="H76" t="n">
-        <v>18907.738275</v>
+        <v>18550.547918</v>
       </c>
       <c r="I76" t="n">
-        <v>19897.56817</v>
+        <v>19671.686079</v>
       </c>
       <c r="J76" t="n">
         <v>20295.883068</v>
@@ -6226,19 +6226,19 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>7102.329899</v>
+        <v>6952.051122</v>
       </c>
       <c r="F77" t="n">
-        <v>7316.597098</v>
+        <v>7244.292722</v>
       </c>
       <c r="G77" t="n">
-        <v>7638.189882</v>
+        <v>7601.578603</v>
       </c>
       <c r="H77" t="n">
-        <v>7473.881448</v>
+        <v>7439.144803</v>
       </c>
       <c r="I77" t="n">
-        <v>7167.571727</v>
+        <v>7138.592507</v>
       </c>
       <c r="J77" t="n">
         <v>6906.544608</v>
@@ -6302,19 +6302,19 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>34622.874589</v>
+        <v>38670.489057</v>
       </c>
       <c r="F78" t="n">
-        <v>35542.697445</v>
+        <v>38308.177977</v>
       </c>
       <c r="G78" t="n">
-        <v>39510.576576</v>
+        <v>41372.953995</v>
       </c>
       <c r="H78" t="n">
-        <v>40502.755544</v>
+        <v>41503.32271</v>
       </c>
       <c r="I78" t="n">
-        <v>39715.613077</v>
+        <v>40118.005267</v>
       </c>
       <c r="J78" t="n">
         <v>38696.144691</v>
@@ -6378,19 +6378,19 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>12189.889669</v>
+        <v>11584.428189</v>
       </c>
       <c r="F79" t="n">
-        <v>13056.55229</v>
+        <v>12608.533821</v>
       </c>
       <c r="G79" t="n">
-        <v>13602.061907</v>
+        <v>13291.19675</v>
       </c>
       <c r="H79" t="n">
-        <v>13237.396245</v>
+        <v>13069.634611</v>
       </c>
       <c r="I79" t="n">
-        <v>12589.965068</v>
+        <v>12525.189242</v>
       </c>
       <c r="J79" t="n">
         <v>12116.142668</v>
@@ -6454,19 +6454,19 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6599.816639</v>
+        <v>6368.320124</v>
       </c>
       <c r="F80" t="n">
-        <v>8357.686626000001</v>
+        <v>8069.706109</v>
       </c>
       <c r="G80" t="n">
-        <v>10283.08915</v>
+        <v>9944.350704</v>
       </c>
       <c r="H80" t="n">
-        <v>11144.445279</v>
+        <v>10860.001486</v>
       </c>
       <c r="I80" t="n">
-        <v>11270.742359</v>
+        <v>11119.812861</v>
       </c>
       <c r="J80" t="n">
         <v>11164.859828</v>
@@ -6530,19 +6530,19 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>15832.961293</v>
+        <v>14831.527769</v>
       </c>
       <c r="F81" t="n">
-        <v>16789.844597</v>
+        <v>15978.712222</v>
       </c>
       <c r="G81" t="n">
-        <v>17385.001437</v>
+        <v>16695.591961</v>
       </c>
       <c r="H81" t="n">
-        <v>16889.230609</v>
+        <v>16411.026253</v>
       </c>
       <c r="I81" t="n">
-        <v>16098.008793</v>
+        <v>15866.51478</v>
       </c>
       <c r="J81" t="n">
         <v>15550.114556</v>
@@ -6606,19 +6606,19 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>10011.219016</v>
+        <v>10409.65871</v>
       </c>
       <c r="F82" t="n">
-        <v>11154.540647</v>
+        <v>11476.410992</v>
       </c>
       <c r="G82" t="n">
-        <v>12686.512679</v>
+        <v>12946.165782</v>
       </c>
       <c r="H82" t="n">
-        <v>12992.207724</v>
+        <v>13164.699636</v>
       </c>
       <c r="I82" t="n">
-        <v>12588.545051</v>
+        <v>12672.557811</v>
       </c>
       <c r="J82" t="n">
         <v>12091.821525</v>
@@ -6682,19 +6682,19 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>62783.420744</v>
+        <v>60659.593331</v>
       </c>
       <c r="F83" t="n">
-        <v>67177.61874200001</v>
+        <v>66043.46281899999</v>
       </c>
       <c r="G83" t="n">
-        <v>71342.545468</v>
+        <v>71104.45487099999</v>
       </c>
       <c r="H83" t="n">
-        <v>69864.346554</v>
+        <v>70167.783541</v>
       </c>
       <c r="I83" t="n">
-        <v>65952.165874</v>
+        <v>66247.545184</v>
       </c>
       <c r="J83" t="n">
         <v>62815.178008</v>
@@ -6910,19 +6910,19 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>13867.268076</v>
+        <v>13810.207082</v>
       </c>
       <c r="F86" t="n">
-        <v>13435.203864</v>
+        <v>13406.817014</v>
       </c>
       <c r="G86" t="n">
-        <v>14032.907662</v>
+        <v>14014.809005</v>
       </c>
       <c r="H86" t="n">
-        <v>13537.127324</v>
+        <v>13526.98118</v>
       </c>
       <c r="I86" t="n">
-        <v>12880.698958</v>
+        <v>12876.317269</v>
       </c>
       <c r="J86" t="n">
         <v>12466.215119</v>
@@ -6986,19 +6986,19 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1594.837577</v>
+        <v>1594.172814</v>
       </c>
       <c r="F87" t="n">
-        <v>1642.486999</v>
+        <v>1643.029218</v>
       </c>
       <c r="G87" t="n">
-        <v>1779.629145</v>
+        <v>1780.983889</v>
       </c>
       <c r="H87" t="n">
-        <v>1783.336385</v>
+        <v>1784.596691</v>
       </c>
       <c r="I87" t="n">
-        <v>1766.837237</v>
+        <v>1767.543544</v>
       </c>
       <c r="J87" t="n">
         <v>1780.864442</v>
@@ -7062,19 +7062,19 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>14020.786495</v>
+        <v>14168.886737</v>
       </c>
       <c r="F88" t="n">
-        <v>15705.672315</v>
+        <v>15749.805327</v>
       </c>
       <c r="G88" t="n">
-        <v>18730.978183</v>
+        <v>18740.739703</v>
       </c>
       <c r="H88" t="n">
-        <v>19793.873973</v>
+        <v>19793.017044</v>
       </c>
       <c r="I88" t="n">
-        <v>19922.496657</v>
+        <v>19920.914517</v>
       </c>
       <c r="J88" t="n">
         <v>20039.397755</v>
@@ -7138,19 +7138,19 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2213.208345</v>
+        <v>2280.452453</v>
       </c>
       <c r="F89" t="n">
-        <v>2217.923008</v>
+        <v>2250.816745</v>
       </c>
       <c r="G89" t="n">
-        <v>2368.522454</v>
+        <v>2390.234948</v>
       </c>
       <c r="H89" t="n">
-        <v>2325.217251</v>
+        <v>2337.885302</v>
       </c>
       <c r="I89" t="n">
-        <v>2251.097175</v>
+        <v>2256.713196</v>
       </c>
       <c r="J89" t="n">
         <v>2230.015286</v>
@@ -7214,19 +7214,19 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>15231.080686</v>
+        <v>15189.717606</v>
       </c>
       <c r="F90" t="n">
-        <v>15593.416821</v>
+        <v>15563.814324</v>
       </c>
       <c r="G90" t="n">
-        <v>16594.562633</v>
+        <v>16575.389464</v>
       </c>
       <c r="H90" t="n">
-        <v>16130.693438</v>
+        <v>16120.739339</v>
       </c>
       <c r="I90" t="n">
-        <v>15405.851888</v>
+        <v>15401.967566</v>
       </c>
       <c r="J90" t="n">
         <v>14996.377844</v>
@@ -7290,19 +7290,19 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5255.184591</v>
+        <v>5260.344946</v>
       </c>
       <c r="F91" t="n">
-        <v>5136.394956</v>
+        <v>5139.29415</v>
       </c>
       <c r="G91" t="n">
-        <v>5362.966129</v>
+        <v>5365.293267</v>
       </c>
       <c r="H91" t="n">
-        <v>5196.063772</v>
+        <v>5197.215271</v>
       </c>
       <c r="I91" t="n">
-        <v>4980.242141</v>
+        <v>4980.502496</v>
       </c>
       <c r="J91" t="n">
         <v>4864.426356</v>
@@ -7366,19 +7366,19 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>3750.622107</v>
+        <v>3714.586953</v>
       </c>
       <c r="F92" t="n">
-        <v>3646.113933</v>
+        <v>3627.434357</v>
       </c>
       <c r="G92" t="n">
-        <v>3712.905186</v>
+        <v>3701.402564</v>
       </c>
       <c r="H92" t="n">
-        <v>3532.009832</v>
+        <v>3525.621512</v>
       </c>
       <c r="I92" t="n">
-        <v>3354.372872</v>
+        <v>3351.572565</v>
       </c>
       <c r="J92" t="n">
         <v>3269.240864</v>
@@ -7442,19 +7442,19 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>522.109282</v>
+        <v>515.384273</v>
       </c>
       <c r="F93" t="n">
-        <v>532.99602</v>
+        <v>529.3066669999999</v>
       </c>
       <c r="G93" t="n">
-        <v>560.8777260000001</v>
+        <v>558.461022</v>
       </c>
       <c r="H93" t="n">
-        <v>536.010687</v>
+        <v>534.655837</v>
       </c>
       <c r="I93" t="n">
-        <v>502.830203</v>
+        <v>502.254635</v>
       </c>
       <c r="J93" t="n">
         <v>480.718264</v>
@@ -7518,19 +7518,19 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>55690.23892</v>
+        <v>55702.945995</v>
       </c>
       <c r="F94" t="n">
-        <v>54507.728671</v>
+        <v>54543.369323</v>
       </c>
       <c r="G94" t="n">
-        <v>58018.028336</v>
+        <v>58050.000227</v>
       </c>
       <c r="H94" t="n">
-        <v>57275.086504</v>
+        <v>57293.646112</v>
       </c>
       <c r="I94" t="n">
-        <v>55599.356947</v>
+        <v>55606.471821</v>
       </c>
       <c r="J94" t="n">
         <v>54655.6155</v>
@@ -7594,19 +7594,19 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>42512.236306</v>
+        <v>42262.665638</v>
       </c>
       <c r="F95" t="n">
-        <v>39777.504783</v>
+        <v>39677.535406</v>
       </c>
       <c r="G95" t="n">
-        <v>39732.500899</v>
+        <v>39688.113783</v>
       </c>
       <c r="H95" t="n">
-        <v>36988.260208</v>
+        <v>36971.887089</v>
       </c>
       <c r="I95" t="n">
-        <v>34239.384672</v>
+        <v>34234.886345</v>
       </c>
       <c r="J95" t="n">
         <v>32437.888505</v>
@@ -7670,19 +7670,19 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>7697.260494</v>
+        <v>7845.806727</v>
       </c>
       <c r="F96" t="n">
-        <v>8153.784844</v>
+        <v>8219.520981</v>
       </c>
       <c r="G96" t="n">
-        <v>9485.365549</v>
+        <v>9518.475715</v>
       </c>
       <c r="H96" t="n">
-        <v>9896.848259</v>
+        <v>9912.25395</v>
       </c>
       <c r="I96" t="n">
-        <v>9867.249451</v>
+        <v>9873.296833</v>
       </c>
       <c r="J96" t="n">
         <v>9804.554273</v>
@@ -7746,19 +7746,19 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2558.906301</v>
+        <v>2568.567956</v>
       </c>
       <c r="F97" t="n">
-        <v>2933.399887</v>
+        <v>2931.882587</v>
       </c>
       <c r="G97" t="n">
-        <v>3534.4472</v>
+        <v>3529.787514</v>
       </c>
       <c r="H97" t="n">
-        <v>3751.736226</v>
+        <v>3747.764534</v>
       </c>
       <c r="I97" t="n">
-        <v>3787.446295</v>
+        <v>3785.423708</v>
       </c>
       <c r="J97" t="n">
         <v>3817.298889</v>
@@ -7822,19 +7822,19 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>13544.864002</v>
+        <v>13581.958373</v>
       </c>
       <c r="F98" t="n">
-        <v>13944.946534</v>
+        <v>13958.320416</v>
       </c>
       <c r="G98" t="n">
-        <v>16059.490316</v>
+        <v>16064.94192</v>
       </c>
       <c r="H98" t="n">
-        <v>17081.104723</v>
+        <v>17082.709717</v>
       </c>
       <c r="I98" t="n">
-        <v>17644.771801</v>
+        <v>17644.920397</v>
       </c>
       <c r="J98" t="n">
         <v>18919.941171</v>
@@ -7898,19 +7898,19 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>17503.293564</v>
+        <v>17570.60131</v>
       </c>
       <c r="F99" t="n">
-        <v>16248.710484</v>
+        <v>16285.709405</v>
       </c>
       <c r="G99" t="n">
-        <v>16644.244482</v>
+        <v>16672.211746</v>
       </c>
       <c r="H99" t="n">
-        <v>16210.031342</v>
+        <v>16228.711037</v>
       </c>
       <c r="I99" t="n">
-        <v>15827.259483</v>
+        <v>15836.595801</v>
       </c>
       <c r="J99" t="n">
         <v>16479.953957</v>
@@ -7974,19 +7974,19 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>9881.316703</v>
+        <v>9873.996956999999</v>
       </c>
       <c r="F100" t="n">
-        <v>10460.608451</v>
+        <v>10454.803716</v>
       </c>
       <c r="G100" t="n">
-        <v>12123.292328</v>
+        <v>12117.821117</v>
       </c>
       <c r="H100" t="n">
-        <v>12934.096344</v>
+        <v>12929.901726</v>
       </c>
       <c r="I100" t="n">
-        <v>13407.065277</v>
+        <v>13404.760136</v>
       </c>
       <c r="J100" t="n">
         <v>14454.901401</v>
@@ -8050,19 +8050,19 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>9547.776598</v>
+        <v>9568.767056999999</v>
       </c>
       <c r="F101" t="n">
-        <v>9472.505823</v>
+        <v>9481.734253000001</v>
       </c>
       <c r="G101" t="n">
-        <v>10380.317169</v>
+        <v>10385.792144</v>
       </c>
       <c r="H101" t="n">
-        <v>10630.938437</v>
+        <v>10633.889968</v>
       </c>
       <c r="I101" t="n">
-        <v>10726.953661</v>
+        <v>10728.179791</v>
       </c>
       <c r="J101" t="n">
         <v>11381.968239</v>
@@ -8126,19 +8126,19 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>113353.351524</v>
+        <v>113272.409371</v>
       </c>
       <c r="F102" t="n">
-        <v>109005.985758</v>
+        <v>108976.373305</v>
       </c>
       <c r="G102" t="n">
-        <v>114201.447098</v>
+        <v>114188.058894</v>
       </c>
       <c r="H102" t="n">
-        <v>112543.740079</v>
+        <v>112538.528227</v>
       </c>
       <c r="I102" t="n">
-        <v>110445.086233</v>
+        <v>110443.579545</v>
       </c>
       <c r="J102" t="n">
         <v>115029.247614</v>
@@ -8202,19 +8202,19 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>147900.440651</v>
+        <v>148042.025273</v>
       </c>
       <c r="F103" t="n">
-        <v>152507.96877</v>
+        <v>152528.76435</v>
       </c>
       <c r="G103" t="n">
-        <v>174148.032492</v>
+        <v>174128.992209</v>
       </c>
       <c r="H103" t="n">
-        <v>182555.777128</v>
+        <v>182528.734304</v>
       </c>
       <c r="I103" t="n">
-        <v>185124.248871</v>
+        <v>185106.542634</v>
       </c>
       <c r="J103" t="n">
         <v>194622.034284</v>
@@ -8278,19 +8278,19 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>21789.512636</v>
+        <v>21772.042776</v>
       </c>
       <c r="F104" t="n">
-        <v>20459.881013</v>
+        <v>20453.049415</v>
       </c>
       <c r="G104" t="n">
-        <v>21000.436873</v>
+        <v>20996.749692</v>
       </c>
       <c r="H104" t="n">
-        <v>20048.542733</v>
+        <v>20046.956593</v>
       </c>
       <c r="I104" t="n">
-        <v>19002.946203</v>
+        <v>19002.489065</v>
       </c>
       <c r="J104" t="n">
         <v>19118.829087</v>
@@ -8354,19 +8354,19 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>7955.107597</v>
+        <v>7950.859451</v>
       </c>
       <c r="F105" t="n">
-        <v>8198.194246999999</v>
+        <v>8195.622665999999</v>
       </c>
       <c r="G105" t="n">
-        <v>9054.276548</v>
+        <v>9052.402688</v>
       </c>
       <c r="H105" t="n">
-        <v>9332.898863</v>
+        <v>9331.617902</v>
       </c>
       <c r="I105" t="n">
-        <v>9547.601156000001</v>
+        <v>9546.898674</v>
       </c>
       <c r="J105" t="n">
         <v>10361.441224</v>
@@ -8430,19 +8430,19 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>117638.649867</v>
+        <v>117494.465753</v>
       </c>
       <c r="F106" t="n">
-        <v>107699.33676</v>
+        <v>107648.564224</v>
       </c>
       <c r="G106" t="n">
-        <v>106418.340145</v>
+        <v>106397.942701</v>
       </c>
       <c r="H106" t="n">
-        <v>99993.035947</v>
+        <v>99986.42791300001</v>
       </c>
       <c r="I106" t="n">
-        <v>94604.407708</v>
+        <v>94603.000377</v>
       </c>
       <c r="J106" t="n">
         <v>95835.90128400001</v>
@@ -8506,19 +8506,19 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>410.347304</v>
+        <v>414.414089</v>
       </c>
       <c r="F107" t="n">
-        <v>396.266344</v>
+        <v>398.46384</v>
       </c>
       <c r="G107" t="n">
-        <v>442.155706</v>
+        <v>443.687057</v>
       </c>
       <c r="H107" t="n">
-        <v>466.091235</v>
+        <v>467.058556</v>
       </c>
       <c r="I107" t="n">
-        <v>484.069289</v>
+        <v>484.543258</v>
       </c>
       <c r="J107" t="n">
         <v>526.7318</v>
@@ -8582,19 +8582,19 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>23989.582028</v>
+        <v>24079.251362</v>
       </c>
       <c r="F108" t="n">
-        <v>23232.409072</v>
+        <v>23274.906003</v>
       </c>
       <c r="G108" t="n">
-        <v>25185.666441</v>
+        <v>25212.515231</v>
       </c>
       <c r="H108" t="n">
-        <v>25600.405393</v>
+        <v>25615.973906</v>
       </c>
       <c r="I108" t="n">
-        <v>25654.372445</v>
+        <v>25661.388869</v>
       </c>
       <c r="J108" t="n">
         <v>26975.084039</v>
@@ -8658,19 +8658,19 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>27325.832287</v>
+        <v>27280.981088</v>
       </c>
       <c r="F109" t="n">
-        <v>26106.246503</v>
+        <v>26086.192902</v>
       </c>
       <c r="G109" t="n">
-        <v>26224.925117</v>
+        <v>26213.926657</v>
       </c>
       <c r="H109" t="n">
-        <v>24306.71275</v>
+        <v>24301.738651</v>
       </c>
       <c r="I109" t="n">
-        <v>22321.754785</v>
+        <v>22320.224961</v>
       </c>
       <c r="J109" t="n">
         <v>21921.992401</v>
@@ -8734,19 +8734,19 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>15255.712089</v>
+        <v>15260.749238</v>
       </c>
       <c r="F110" t="n">
-        <v>14770.137181</v>
+        <v>14774.300199</v>
       </c>
       <c r="G110" t="n">
-        <v>15652.272154</v>
+        <v>15656.265885</v>
       </c>
       <c r="H110" t="n">
-        <v>15670.343869</v>
+        <v>15673.254622</v>
       </c>
       <c r="I110" t="n">
-        <v>15683.19478</v>
+        <v>15684.648088</v>
       </c>
       <c r="J110" t="n">
         <v>16727.596755</v>
@@ -8810,19 +8810,19 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>90213.400585</v>
+        <v>90174.719769</v>
       </c>
       <c r="F111" t="n">
-        <v>85791.279591</v>
+        <v>85780.926703</v>
       </c>
       <c r="G111" t="n">
-        <v>89402.172699</v>
+        <v>89399.28043100001</v>
       </c>
       <c r="H111" t="n">
-        <v>87788.724147</v>
+        <v>87788.42456499999</v>
       </c>
       <c r="I111" t="n">
-        <v>85877.467714</v>
+        <v>85877.746749</v>
       </c>
       <c r="J111" t="n">
         <v>89230.25824900001</v>
@@ -8886,19 +8886,19 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>104875.150386</v>
+        <v>104847.095955</v>
       </c>
       <c r="F112" t="n">
-        <v>100641.078426</v>
+        <v>100637.823562</v>
       </c>
       <c r="G112" t="n">
-        <v>104659.19047</v>
+        <v>104665.671665</v>
       </c>
       <c r="H112" t="n">
-        <v>102289.61105</v>
+        <v>102298.126352</v>
       </c>
       <c r="I112" t="n">
-        <v>99608.68363499999</v>
+        <v>99614.364698</v>
       </c>
       <c r="J112" t="n">
         <v>103204.947696</v>
@@ -8962,58 +8962,58 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>14145.314283</v>
+        <v>14487.494759</v>
       </c>
       <c r="F113" t="n">
-        <v>15559.084878</v>
+        <v>15593.303798</v>
       </c>
       <c r="G113" t="n">
-        <v>14241.727596</v>
+        <v>13840.733055</v>
       </c>
       <c r="H113" t="n">
-        <v>13821.968754</v>
+        <v>13151.730679</v>
       </c>
       <c r="I113" t="n">
-        <v>13324.336297</v>
+        <v>12549.019094</v>
       </c>
       <c r="J113" t="n">
-        <v>13095.98329</v>
+        <v>12309.502432</v>
       </c>
       <c r="K113" t="n">
-        <v>12586.868633</v>
+        <v>11859.095305</v>
       </c>
       <c r="L113" t="n">
-        <v>11746.504131</v>
+        <v>11108.099063</v>
       </c>
       <c r="M113" t="n">
-        <v>10725.510697</v>
+        <v>10177.263091</v>
       </c>
       <c r="N113" t="n">
-        <v>9607.764886000001</v>
+        <v>9141.467092999999</v>
       </c>
       <c r="O113" t="n">
-        <v>8498.649237</v>
+        <v>8103.131702</v>
       </c>
       <c r="P113" t="n">
-        <v>7431.285895</v>
+        <v>7098.04459</v>
       </c>
       <c r="Q113" t="n">
-        <v>6382.684016</v>
+        <v>6107.015006</v>
       </c>
       <c r="R113" t="n">
-        <v>5379.326904</v>
+        <v>5156.614069</v>
       </c>
       <c r="S113" t="n">
-        <v>4446.352985</v>
+        <v>4271.510433</v>
       </c>
       <c r="T113" t="n">
-        <v>3597.680636</v>
+        <v>3465.315813</v>
       </c>
       <c r="U113" t="n">
-        <v>2878.575219</v>
+        <v>2781.877362</v>
       </c>
       <c r="V113" t="n">
-        <v>2315.085473</v>
+        <v>2246.204319</v>
       </c>
     </row>
     <row r="114">
@@ -9038,58 +9038,58 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6485.977919</v>
+        <v>5685.843064</v>
       </c>
       <c r="F114" t="n">
-        <v>6784.475947</v>
+        <v>6113.492616</v>
       </c>
       <c r="G114" t="n">
-        <v>5468.982675</v>
+        <v>5018.088956</v>
       </c>
       <c r="H114" t="n">
-        <v>4816.399683</v>
+        <v>4491.489051</v>
       </c>
       <c r="I114" t="n">
-        <v>4305.904057</v>
+        <v>4062.246154</v>
       </c>
       <c r="J114" t="n">
-        <v>3970.068532</v>
+        <v>3772.648466</v>
       </c>
       <c r="K114" t="n">
-        <v>3604.904774</v>
+        <v>3441.54157</v>
       </c>
       <c r="L114" t="n">
-        <v>3194.835369</v>
+        <v>3059.293125</v>
       </c>
       <c r="M114" t="n">
-        <v>2778.047547</v>
+        <v>2665.845788</v>
       </c>
       <c r="N114" t="n">
-        <v>2372.47987</v>
+        <v>2280.066245</v>
       </c>
       <c r="O114" t="n">
-        <v>2007.809394</v>
+        <v>1931.580217</v>
       </c>
       <c r="P114" t="n">
-        <v>1681.62883</v>
+        <v>1619.414209</v>
       </c>
       <c r="Q114" t="n">
-        <v>1382.88225</v>
+        <v>1333.403021</v>
       </c>
       <c r="R114" t="n">
-        <v>1115.502344</v>
+        <v>1077.245324</v>
       </c>
       <c r="S114" t="n">
-        <v>883.117877</v>
+        <v>854.37689</v>
       </c>
       <c r="T114" t="n">
-        <v>686.866054</v>
+        <v>665.914452</v>
       </c>
       <c r="U114" t="n">
-        <v>533.628891</v>
+        <v>518.610784</v>
       </c>
       <c r="V114" t="n">
-        <v>420.525021</v>
+        <v>409.879384</v>
       </c>
     </row>
     <row r="115">
@@ -9114,58 +9114,58 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>87752.28819399999</v>
+        <v>88210.242574</v>
       </c>
       <c r="F115" t="n">
-        <v>97476.306102</v>
+        <v>98113.07051400001</v>
       </c>
       <c r="G115" t="n">
-        <v>88656.806428</v>
+        <v>89508.694687</v>
       </c>
       <c r="H115" t="n">
-        <v>84741.617721</v>
+        <v>85736.766427</v>
       </c>
       <c r="I115" t="n">
-        <v>79894.498345</v>
+        <v>80913.47345200001</v>
       </c>
       <c r="J115" t="n">
-        <v>76754.83919499999</v>
+        <v>77738.74011899999</v>
       </c>
       <c r="K115" t="n">
-        <v>72464.531343</v>
+        <v>73355.66787600001</v>
       </c>
       <c r="L115" t="n">
-        <v>66893.901317</v>
+        <v>67667.84862999999</v>
       </c>
       <c r="M115" t="n">
-        <v>60802.654065</v>
+        <v>61463.10343</v>
       </c>
       <c r="N115" t="n">
-        <v>54479.523919</v>
+        <v>55038.235337</v>
       </c>
       <c r="O115" t="n">
-        <v>48269.488926</v>
+        <v>48741.235639</v>
       </c>
       <c r="P115" t="n">
-        <v>42276.802464</v>
+        <v>42672.258389</v>
       </c>
       <c r="Q115" t="n">
-        <v>36337.585877</v>
+        <v>36662.734116</v>
       </c>
       <c r="R115" t="n">
-        <v>30607.603724</v>
+        <v>30868.573579</v>
       </c>
       <c r="S115" t="n">
-        <v>25243.367414</v>
+        <v>25446.950953</v>
       </c>
       <c r="T115" t="n">
-        <v>20363.498772</v>
+        <v>20516.815197</v>
       </c>
       <c r="U115" t="n">
-        <v>16282.868306</v>
+        <v>16394.58427</v>
       </c>
       <c r="V115" t="n">
-        <v>13030.103115</v>
+        <v>13109.629906</v>
       </c>
     </row>
     <row r="116">
@@ -9190,19 +9190,19 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>5660.954762</v>
+        <v>5462.358011</v>
       </c>
       <c r="F116" t="n">
-        <v>6249.333237</v>
+        <v>6122.89211</v>
       </c>
       <c r="G116" t="n">
-        <v>6390.210033</v>
+        <v>6304.537138</v>
       </c>
       <c r="H116" t="n">
-        <v>6430.497806</v>
+        <v>6375.819531</v>
       </c>
       <c r="I116" t="n">
-        <v>6456.601231</v>
+        <v>6429.615393</v>
       </c>
       <c r="J116" t="n">
         <v>6613.428321</v>
@@ -9266,19 +9266,19 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>5098.929168</v>
+        <v>5078.360003</v>
       </c>
       <c r="F117" t="n">
-        <v>4988.837695</v>
+        <v>5013.532095</v>
       </c>
       <c r="G117" t="n">
-        <v>4773.319802</v>
+        <v>4800.654282</v>
       </c>
       <c r="H117" t="n">
-        <v>4581.780046</v>
+        <v>4601.961292</v>
       </c>
       <c r="I117" t="n">
-        <v>4423.160089</v>
+        <v>4433.455083</v>
       </c>
       <c r="J117" t="n">
         <v>4369.712523</v>
@@ -9342,19 +9342,19 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5117.318672</v>
+        <v>5189.122906</v>
       </c>
       <c r="F118" t="n">
-        <v>5118.638453</v>
+        <v>5154.761154</v>
       </c>
       <c r="G118" t="n">
-        <v>5076.420355</v>
+        <v>5093.093101</v>
       </c>
       <c r="H118" t="n">
-        <v>5035.330645</v>
+        <v>5041.835054</v>
       </c>
       <c r="I118" t="n">
-        <v>5006.665366</v>
+        <v>5008.284627</v>
       </c>
       <c r="J118" t="n">
         <v>5091.254226</v>
@@ -9418,19 +9418,19 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>2776.696941</v>
+        <v>2734.966219</v>
       </c>
       <c r="F119" t="n">
-        <v>2870.01107</v>
+        <v>2854.61832</v>
       </c>
       <c r="G119" t="n">
-        <v>2823.519233</v>
+        <v>2819.507011</v>
       </c>
       <c r="H119" t="n">
-        <v>2775.024688</v>
+        <v>2775.436116</v>
       </c>
       <c r="I119" t="n">
-        <v>2752.669999</v>
+        <v>2753.758277</v>
       </c>
       <c r="J119" t="n">
         <v>2809.88366</v>
@@ -9494,19 +9494,19 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>690.522794</v>
+        <v>654.398539</v>
       </c>
       <c r="F120" t="n">
-        <v>793.255646</v>
+        <v>769.990287</v>
       </c>
       <c r="G120" t="n">
-        <v>829.43647</v>
+        <v>813.4642689999999</v>
       </c>
       <c r="H120" t="n">
-        <v>851.771837</v>
+        <v>841.439752</v>
       </c>
       <c r="I120" t="n">
-        <v>873.032152</v>
+        <v>867.864674</v>
       </c>
       <c r="J120" t="n">
         <v>913.360289</v>
@@ -9570,19 +9570,19 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>10783.673796</v>
+        <v>10219.532854</v>
       </c>
       <c r="F121" t="n">
-        <v>11510.81066</v>
+        <v>11173.210619</v>
       </c>
       <c r="G121" t="n">
-        <v>11378.638147</v>
+        <v>11159.523238</v>
       </c>
       <c r="H121" t="n">
-        <v>11285.420821</v>
+        <v>11148.527444</v>
       </c>
       <c r="I121" t="n">
-        <v>11361.798268</v>
+        <v>11294.547775</v>
       </c>
       <c r="J121" t="n">
         <v>11812.821147</v>
@@ -9646,19 +9646,19 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>106054.651016</v>
+        <v>106844.008615</v>
       </c>
       <c r="F122" t="n">
-        <v>112464.537968</v>
+        <v>112906.420145</v>
       </c>
       <c r="G122" t="n">
-        <v>115462.411188</v>
+        <v>115743.176191</v>
       </c>
       <c r="H122" t="n">
-        <v>117320.324761</v>
+        <v>117495.131416</v>
       </c>
       <c r="I122" t="n">
-        <v>118847.157686</v>
+        <v>118933.558962</v>
       </c>
       <c r="J122" t="n">
         <v>122432.089104</v>
@@ -9722,19 +9722,19 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>896.959485</v>
+        <v>901.529735</v>
       </c>
       <c r="F123" t="n">
-        <v>908.830206</v>
+        <v>911.134393</v>
       </c>
       <c r="G123" t="n">
-        <v>943.1092159999999</v>
+        <v>944.692182</v>
       </c>
       <c r="H123" t="n">
-        <v>922.011987</v>
+        <v>923.009798</v>
       </c>
       <c r="I123" t="n">
-        <v>904.964963</v>
+        <v>905.459656</v>
       </c>
       <c r="J123" t="n">
         <v>941.962032</v>
@@ -9798,19 +9798,19 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>10783.116091</v>
+        <v>10851.834483</v>
       </c>
       <c r="F124" t="n">
-        <v>10710.375966</v>
+        <v>10744.700892</v>
       </c>
       <c r="G124" t="n">
-        <v>11139.244027</v>
+        <v>11161.538095</v>
       </c>
       <c r="H124" t="n">
-        <v>11012.036201</v>
+        <v>11025.264497</v>
       </c>
       <c r="I124" t="n">
-        <v>10992.847379</v>
+        <v>10998.970271</v>
       </c>
       <c r="J124" t="n">
         <v>11654.692871</v>
@@ -9874,19 +9874,19 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>19099.574725</v>
+        <v>19026.286083</v>
       </c>
       <c r="F125" t="n">
-        <v>19715.463147</v>
+        <v>19678.834034</v>
       </c>
       <c r="G125" t="n">
-        <v>21132.846942</v>
+        <v>21108.969909</v>
       </c>
       <c r="H125" t="n">
-        <v>21154.619185</v>
+        <v>21140.393077</v>
       </c>
       <c r="I125" t="n">
-        <v>21083.382136</v>
+        <v>21076.76455</v>
       </c>
       <c r="J125" t="n">
         <v>22093.638258</v>
@@ -10254,19 +10254,19 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>34020.435452</v>
+        <v>37590.718872</v>
       </c>
       <c r="F130" t="n">
-        <v>29117.786299</v>
+        <v>31975.621407</v>
       </c>
       <c r="G130" t="n">
-        <v>28191.739631</v>
+        <v>30528.409923</v>
       </c>
       <c r="H130" t="n">
-        <v>26907.11191</v>
+        <v>28640.604432</v>
       </c>
       <c r="I130" t="n">
-        <v>25341.949636</v>
+        <v>26320.868713</v>
       </c>
       <c r="J130" t="n">
         <v>23618.660497</v>
@@ -10330,19 +10330,19 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>4137.96047</v>
+        <v>4367.063687</v>
       </c>
       <c r="F131" t="n">
-        <v>4265.973664</v>
+        <v>4478.950498</v>
       </c>
       <c r="G131" t="n">
-        <v>4600.4212</v>
+        <v>4768.572154</v>
       </c>
       <c r="H131" t="n">
-        <v>4860.07691</v>
+        <v>4976.80024</v>
       </c>
       <c r="I131" t="n">
-        <v>5147.180379</v>
+        <v>5209.728952</v>
       </c>
       <c r="J131" t="n">
         <v>5513.568878</v>
@@ -10406,19 +10406,19 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>174787.232324</v>
+        <v>173306.682438</v>
       </c>
       <c r="F132" t="n">
-        <v>194602.486396</v>
+        <v>193138.047022</v>
       </c>
       <c r="G132" t="n">
-        <v>217113.02113</v>
+        <v>215570.896923</v>
       </c>
       <c r="H132" t="n">
-        <v>231879.80996</v>
+        <v>230573.789134</v>
       </c>
       <c r="I132" t="n">
-        <v>244969.147303</v>
+        <v>244221.352605</v>
       </c>
       <c r="J132" t="n">
         <v>260013.351927</v>
@@ -10482,19 +10482,19 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>86987.557938</v>
+        <v>83828.637288</v>
       </c>
       <c r="F133" t="n">
-        <v>101192.905885</v>
+        <v>99831.8152</v>
       </c>
       <c r="G133" t="n">
-        <v>112000.331044</v>
+        <v>111747.90555</v>
       </c>
       <c r="H133" t="n">
-        <v>119477.699654</v>
+        <v>119651.978304</v>
       </c>
       <c r="I133" t="n">
-        <v>128877.901824</v>
+        <v>129029.729938</v>
       </c>
       <c r="J133" t="n">
         <v>142219.546506</v>
@@ -10558,19 +10558,19 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>12843.743752</v>
+        <v>12481.610343</v>
       </c>
       <c r="F134" t="n">
-        <v>16568.03286</v>
+        <v>16177.894028</v>
       </c>
       <c r="G134" t="n">
-        <v>20983.776846</v>
+        <v>20593.99783</v>
       </c>
       <c r="H134" t="n">
-        <v>24956.713947</v>
+        <v>24634.320292</v>
       </c>
       <c r="I134" t="n">
-        <v>29033.545713</v>
+        <v>28839.998193</v>
       </c>
       <c r="J134" t="n">
         <v>33887.391361</v>
@@ -10634,19 +10634,19 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>16184.793742</v>
+        <v>15231.048182</v>
       </c>
       <c r="F135" t="n">
-        <v>20738.549768</v>
+        <v>20021.345221</v>
       </c>
       <c r="G135" t="n">
-        <v>24501.931866</v>
+        <v>23959.137235</v>
       </c>
       <c r="H135" t="n">
-        <v>27358.175482</v>
+        <v>26982.243055</v>
       </c>
       <c r="I135" t="n">
-        <v>30398.411332</v>
+        <v>30195.622984</v>
       </c>
       <c r="J135" t="n">
         <v>34249.262859</v>
@@ -10710,19 +10710,19 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>11097.142234</v>
+        <v>12211.221626</v>
       </c>
       <c r="F136" t="n">
-        <v>9099.374276</v>
+        <v>9815.734741</v>
       </c>
       <c r="G136" t="n">
-        <v>9000.704976000001</v>
+        <v>9408.631730999999</v>
       </c>
       <c r="H136" t="n">
-        <v>9527.487297</v>
+        <v>9728.313423</v>
       </c>
       <c r="I136" t="n">
-        <v>10430.876293</v>
+        <v>10512.581054</v>
       </c>
       <c r="J136" t="n">
         <v>11564.159737</v>
@@ -10786,19 +10786,19 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>7305.044238</v>
+        <v>6961.370188</v>
       </c>
       <c r="F137" t="n">
-        <v>8718.875216</v>
+        <v>8461.897777</v>
       </c>
       <c r="G137" t="n">
-        <v>10065.429091</v>
+        <v>9857.716898999999</v>
       </c>
       <c r="H137" t="n">
-        <v>10983.256188</v>
+        <v>10833.210471</v>
       </c>
       <c r="I137" t="n">
-        <v>11783.215535</v>
+        <v>11702.094562</v>
       </c>
       <c r="J137" t="n">
         <v>12698.463182</v>
@@ -10862,19 +10862,19 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>12396.010555</v>
+        <v>13540.001968</v>
       </c>
       <c r="F138" t="n">
-        <v>10412.162614</v>
+        <v>11221.287815</v>
       </c>
       <c r="G138" t="n">
-        <v>10077.383824</v>
+        <v>10638.49749</v>
       </c>
       <c r="H138" t="n">
-        <v>9912.690586000001</v>
+        <v>10256.362428</v>
       </c>
       <c r="I138" t="n">
-        <v>10009.559941</v>
+        <v>10170.153239</v>
       </c>
       <c r="J138" t="n">
         <v>10430.532273</v>
@@ -10938,19 +10938,19 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>22991.942973</v>
+        <v>25981.610349</v>
       </c>
       <c r="F139" t="n">
-        <v>17580.251858</v>
+        <v>19932.734641</v>
       </c>
       <c r="G139" t="n">
-        <v>15611.38207</v>
+        <v>17514.082648</v>
       </c>
       <c r="H139" t="n">
-        <v>13739.460788</v>
+        <v>15140.286688</v>
       </c>
       <c r="I139" t="n">
-        <v>11710.489911</v>
+        <v>12497.27572</v>
       </c>
       <c r="J139" t="n">
         <v>9416.305692</v>
@@ -11014,19 +11014,19 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>94421.53597300001</v>
+        <v>100507.096783</v>
       </c>
       <c r="F140" t="n">
-        <v>89315.09789999999</v>
+        <v>92884.093081</v>
       </c>
       <c r="G140" t="n">
-        <v>97124.18578</v>
+        <v>99169.31576500001</v>
       </c>
       <c r="H140" t="n">
-        <v>105303.751132</v>
+        <v>106425.411929</v>
       </c>
       <c r="I140" t="n">
-        <v>114134.876478</v>
+        <v>114660.163844</v>
       </c>
       <c r="J140" t="n">
         <v>124621.673848</v>
@@ -11090,19 +11090,19 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>52680.063297</v>
+        <v>49064.895952</v>
       </c>
       <c r="F141" t="n">
-        <v>67262.15145799999</v>
+        <v>64515.804982</v>
       </c>
       <c r="G141" t="n">
-        <v>79019.481572</v>
+        <v>76891.463726</v>
       </c>
       <c r="H141" t="n">
-        <v>87229.824026</v>
+        <v>85739.541187</v>
       </c>
       <c r="I141" t="n">
-        <v>94969.244433</v>
+        <v>94172.159977</v>
       </c>
       <c r="J141" t="n">
         <v>103973.227111</v>
@@ -11166,19 +11166,19 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>73686.323534</v>
+        <v>68467.828805</v>
       </c>
       <c r="F142" t="n">
-        <v>87524.016858</v>
+        <v>83942.43863999999</v>
       </c>
       <c r="G142" t="n">
-        <v>92308.327126</v>
+        <v>89949.48828000001</v>
       </c>
       <c r="H142" t="n">
-        <v>95072.404876</v>
+        <v>93625.601172</v>
       </c>
       <c r="I142" t="n">
-        <v>101439.062547</v>
+        <v>100713.731542</v>
       </c>
       <c r="J142" t="n">
         <v>113686.802817</v>
@@ -11470,58 +11470,58 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>795.136695</v>
+        <v>729.771911</v>
       </c>
       <c r="F146" t="n">
-        <v>1022.062509</v>
+        <v>945.441286</v>
       </c>
       <c r="G146" t="n">
-        <v>1142.206874</v>
+        <v>1058.554004</v>
       </c>
       <c r="H146" t="n">
-        <v>1153.966007</v>
+        <v>1071.95994</v>
       </c>
       <c r="I146" t="n">
-        <v>1074.554872</v>
+        <v>1002.293086</v>
       </c>
       <c r="J146" t="n">
-        <v>991.781087</v>
+        <v>928.926433</v>
       </c>
       <c r="K146" t="n">
-        <v>940.5781050000001</v>
+        <v>884.316713</v>
       </c>
       <c r="L146" t="n">
-        <v>896.488707</v>
+        <v>845.856886</v>
       </c>
       <c r="M146" t="n">
-        <v>839.637155</v>
+        <v>794.93036</v>
       </c>
       <c r="N146" t="n">
-        <v>763.442311</v>
+        <v>724.977131</v>
       </c>
       <c r="O146" t="n">
-        <v>674.115346</v>
+        <v>641.784225</v>
       </c>
       <c r="P146" t="n">
-        <v>593.570093</v>
+        <v>566.366167</v>
       </c>
       <c r="Q146" t="n">
-        <v>533.5551830000001</v>
+        <v>510.199331</v>
       </c>
       <c r="R146" t="n">
-        <v>486.548501</v>
+        <v>466.301156</v>
       </c>
       <c r="S146" t="n">
-        <v>446.52798</v>
+        <v>429.028414</v>
       </c>
       <c r="T146" t="n">
-        <v>404.488556</v>
+        <v>389.766997</v>
       </c>
       <c r="U146" t="n">
-        <v>347.091519</v>
+        <v>335.637294</v>
       </c>
       <c r="V146" t="n">
-        <v>281.804011</v>
+        <v>273.68057</v>
       </c>
     </row>
     <row r="147">
@@ -11546,58 +11546,58 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>359.558286</v>
+        <v>331.237859</v>
       </c>
       <c r="F147" t="n">
-        <v>454.838124</v>
+        <v>422.540889</v>
       </c>
       <c r="G147" t="n">
-        <v>511.738412</v>
+        <v>476.242868</v>
       </c>
       <c r="H147" t="n">
-        <v>537.6493819999999</v>
+        <v>501.128598</v>
       </c>
       <c r="I147" t="n">
-        <v>527.9755270000001</v>
+        <v>493.706741</v>
       </c>
       <c r="J147" t="n">
-        <v>517.165225</v>
+        <v>485.194466</v>
       </c>
       <c r="K147" t="n">
-        <v>520.932806</v>
+        <v>490.201342</v>
       </c>
       <c r="L147" t="n">
-        <v>527.1881509999999</v>
+        <v>497.483469</v>
       </c>
       <c r="M147" t="n">
-        <v>522.250822</v>
+        <v>494.220069</v>
       </c>
       <c r="N147" t="n">
-        <v>499.997517</v>
+        <v>474.392014</v>
       </c>
       <c r="O147" t="n">
-        <v>460.859622</v>
+        <v>438.266542</v>
       </c>
       <c r="P147" t="n">
-        <v>420.793083</v>
+        <v>401.00417</v>
       </c>
       <c r="Q147" t="n">
-        <v>390.406656</v>
+        <v>372.821699</v>
       </c>
       <c r="R147" t="n">
-        <v>366.049851</v>
+        <v>350.344823</v>
       </c>
       <c r="S147" t="n">
-        <v>344.511209</v>
+        <v>330.574558</v>
       </c>
       <c r="T147" t="n">
-        <v>319.595477</v>
+        <v>307.581593</v>
       </c>
       <c r="U147" t="n">
-        <v>280.672254</v>
+        <v>271.100379</v>
       </c>
       <c r="V147" t="n">
-        <v>232.137821</v>
+        <v>225.214323</v>
       </c>
     </row>
     <row r="148">
@@ -11622,58 +11622,58 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>51212.851222</v>
+        <v>51306.536433</v>
       </c>
       <c r="F148" t="n">
-        <v>54932.739528</v>
+        <v>55041.657986</v>
       </c>
       <c r="G148" t="n">
-        <v>58869.686399</v>
+        <v>58988.834813</v>
       </c>
       <c r="H148" t="n">
-        <v>59890.89861</v>
+        <v>60009.425461</v>
       </c>
       <c r="I148" t="n">
-        <v>57278.323309</v>
+        <v>57384.853882</v>
       </c>
       <c r="J148" t="n">
-        <v>55041.139665</v>
+        <v>55135.965079</v>
       </c>
       <c r="K148" t="n">
-        <v>54621.588644</v>
+        <v>54708.581501</v>
       </c>
       <c r="L148" t="n">
-        <v>54527.627136</v>
+        <v>54607.96364</v>
       </c>
       <c r="M148" t="n">
-        <v>53349.216503</v>
+        <v>53421.954051</v>
       </c>
       <c r="N148" t="n">
-        <v>50503.817494</v>
+        <v>50567.888177</v>
       </c>
       <c r="O148" t="n">
-        <v>46014.199728</v>
+        <v>46069.123929</v>
       </c>
       <c r="P148" t="n">
-        <v>41469.307995</v>
+        <v>41516.300834</v>
       </c>
       <c r="Q148" t="n">
-        <v>37879.052732</v>
+        <v>37919.99354</v>
       </c>
       <c r="R148" t="n">
-        <v>34857.7426</v>
+        <v>34893.694972</v>
       </c>
       <c r="S148" t="n">
-        <v>32049.459185</v>
+        <v>32080.895403</v>
       </c>
       <c r="T148" t="n">
-        <v>28808.795965</v>
+        <v>28835.531409</v>
       </c>
       <c r="U148" t="n">
-        <v>24311.362965</v>
+        <v>24332.389065</v>
       </c>
       <c r="V148" t="n">
-        <v>19239.35335</v>
+        <v>19254.400288</v>
       </c>
     </row>
     <row r="149">
@@ -11698,19 +11698,19 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6595.460328</v>
+        <v>6291.61749</v>
       </c>
       <c r="F149" t="n">
-        <v>8101.389725</v>
+        <v>7757.694701</v>
       </c>
       <c r="G149" t="n">
-        <v>9674.144925000001</v>
+        <v>9347.205905000001</v>
       </c>
       <c r="H149" t="n">
-        <v>10974.381115</v>
+        <v>10721.851096</v>
       </c>
       <c r="I149" t="n">
-        <v>12272.456911</v>
+        <v>12134.983079</v>
       </c>
       <c r="J149" t="n">
         <v>13657.071579</v>
@@ -11774,19 +11774,19 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>16297.985638</v>
+        <v>17303.724748</v>
       </c>
       <c r="F150" t="n">
-        <v>15927.293443</v>
+        <v>16879.125959</v>
       </c>
       <c r="G150" t="n">
-        <v>16615.653505</v>
+        <v>17449.958797</v>
       </c>
       <c r="H150" t="n">
-        <v>17060.99034</v>
+        <v>17710.122885</v>
       </c>
       <c r="I150" t="n">
-        <v>17574.723549</v>
+        <v>17961.736801</v>
       </c>
       <c r="J150" t="n">
         <v>18217.556329</v>
@@ -11850,19 +11850,19 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>10514.400788</v>
+        <v>10473.238487</v>
       </c>
       <c r="F151" t="n">
-        <v>12073.302433</v>
+        <v>12053.593719</v>
       </c>
       <c r="G151" t="n">
-        <v>13818.539089</v>
+        <v>13839.669384</v>
       </c>
       <c r="H151" t="n">
-        <v>15156.751825</v>
+        <v>15197.191894</v>
       </c>
       <c r="I151" t="n">
-        <v>16547.985447</v>
+        <v>16578.898366</v>
       </c>
       <c r="J151" t="n">
         <v>18109.643648</v>
@@ -11926,19 +11926,19 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>19255.613957</v>
+        <v>19072.220275</v>
       </c>
       <c r="F152" t="n">
-        <v>21957.559824</v>
+        <v>21874.056584</v>
       </c>
       <c r="G152" t="n">
-        <v>24591.383216</v>
+        <v>24530.353528</v>
       </c>
       <c r="H152" t="n">
-        <v>26517.15653</v>
+        <v>26453.72143</v>
       </c>
       <c r="I152" t="n">
-        <v>28604.52822</v>
+        <v>28551.704981</v>
       </c>
       <c r="J152" t="n">
         <v>31133.672274</v>
@@ -12002,19 +12002,19 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>3181.008607</v>
+        <v>2746.210658</v>
       </c>
       <c r="F153" t="n">
-        <v>4576.126207</v>
+        <v>4103.51755</v>
       </c>
       <c r="G153" t="n">
-        <v>5861.171816</v>
+        <v>5420.411839</v>
       </c>
       <c r="H153" t="n">
-        <v>6946.831696</v>
+        <v>6596.449544</v>
       </c>
       <c r="I153" t="n">
-        <v>8085.358654</v>
+        <v>7874.326974</v>
       </c>
       <c r="J153" t="n">
         <v>9408.781599</v>
@@ -12078,19 +12078,19 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1890.510894</v>
+        <v>1847.968554</v>
       </c>
       <c r="F154" t="n">
-        <v>2148.617226</v>
+        <v>2116.300345</v>
       </c>
       <c r="G154" t="n">
-        <v>2386.839247</v>
+        <v>2360.132344</v>
       </c>
       <c r="H154" t="n">
-        <v>2554.271326</v>
+        <v>2531.045983</v>
       </c>
       <c r="I154" t="n">
-        <v>2743.965327</v>
+        <v>2727.367906</v>
       </c>
       <c r="J154" t="n">
         <v>2989.9366</v>
@@ -12154,19 +12154,19 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>3066.607322</v>
+        <v>2975.138819</v>
       </c>
       <c r="F155" t="n">
-        <v>4781.502861</v>
+        <v>4533.650921</v>
       </c>
       <c r="G155" t="n">
-        <v>6911.897463</v>
+        <v>6440.571841</v>
       </c>
       <c r="H155" t="n">
-        <v>10108.260857</v>
+        <v>9329.620661000001</v>
       </c>
       <c r="I155" t="n">
-        <v>15102.762056</v>
+        <v>14032.250843</v>
       </c>
       <c r="J155" t="n">
         <v>23079.464377</v>
@@ -12230,19 +12230,19 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>26081.366977</v>
+        <v>26220.931287</v>
       </c>
       <c r="F156" t="n">
-        <v>36140.057885</v>
+        <v>36511.412546</v>
       </c>
       <c r="G156" t="n">
-        <v>46028.269003</v>
+        <v>46718.203537</v>
       </c>
       <c r="H156" t="n">
-        <v>58232.172546</v>
+        <v>59338.848306</v>
       </c>
       <c r="I156" t="n">
-        <v>72459.430461</v>
+        <v>73910.653299</v>
       </c>
       <c r="J156" t="n">
         <v>84594.50444600001</v>
@@ -12306,19 +12306,19 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>766.851257</v>
+        <v>799.818567</v>
       </c>
       <c r="F157" t="n">
-        <v>1188.753201</v>
+        <v>1293.231004</v>
       </c>
       <c r="G157" t="n">
-        <v>1520.65655</v>
+        <v>1730.999793</v>
       </c>
       <c r="H157" t="n">
-        <v>1696.653567</v>
+        <v>2032.175324</v>
       </c>
       <c r="I157" t="n">
-        <v>1567.974277</v>
+        <v>1990.768232</v>
       </c>
       <c r="J157" t="n">
         <v>653.307103</v>
@@ -12382,19 +12382,19 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>2512.101518</v>
+        <v>2439.871003</v>
       </c>
       <c r="F158" t="n">
-        <v>3325.863477</v>
+        <v>3129.767276</v>
       </c>
       <c r="G158" t="n">
-        <v>4175.171251</v>
+        <v>3809.466433</v>
       </c>
       <c r="H158" t="n">
-        <v>5541.212069</v>
+        <v>4961.39723</v>
       </c>
       <c r="I158" t="n">
-        <v>7813.333169</v>
+        <v>7058.075069</v>
       </c>
       <c r="J158" t="n">
         <v>11687.180528</v>
@@ -12458,19 +12458,19 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>181.054876</v>
+        <v>187.413221</v>
       </c>
       <c r="F159" t="n">
-        <v>220.793142</v>
+        <v>235.311697</v>
       </c>
       <c r="G159" t="n">
-        <v>248.886364</v>
+        <v>272.590128</v>
       </c>
       <c r="H159" t="n">
-        <v>274.196477</v>
+        <v>308.105214</v>
       </c>
       <c r="I159" t="n">
-        <v>283.421182</v>
+        <v>324.087144</v>
       </c>
       <c r="J159" t="n">
         <v>224.926772</v>
@@ -12534,19 +12534,19 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>4423.405741</v>
+        <v>4408.214794</v>
       </c>
       <c r="F160" t="n">
-        <v>6272.263039</v>
+        <v>6225.860161</v>
       </c>
       <c r="G160" t="n">
-        <v>8307.707544000001</v>
+        <v>8220.756442</v>
       </c>
       <c r="H160" t="n">
-        <v>11159.523288</v>
+        <v>11041.872068</v>
       </c>
       <c r="I160" t="n">
-        <v>15077.419697</v>
+        <v>14988.506256</v>
       </c>
       <c r="J160" t="n">
         <v>19432.211214</v>
@@ -12686,19 +12686,19 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>2563.371573</v>
+        <v>2886.039912</v>
       </c>
       <c r="F162" t="n">
-        <v>1531.595936</v>
+        <v>1779.662686</v>
       </c>
       <c r="G162" t="n">
-        <v>1033.483844</v>
+        <v>1186.63967</v>
       </c>
       <c r="H162" t="n">
-        <v>848.942435</v>
+        <v>943.777381</v>
       </c>
       <c r="I162" t="n">
-        <v>773.226659</v>
+        <v>824.025924</v>
       </c>
       <c r="J162" t="n">
         <v>730.9092460000001</v>
@@ -12762,19 +12762,19 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>513.15455</v>
+        <v>466.40941</v>
       </c>
       <c r="F163" t="n">
-        <v>696.669295</v>
+        <v>641.977068</v>
       </c>
       <c r="G163" t="n">
-        <v>820.407062</v>
+        <v>771.697949</v>
       </c>
       <c r="H163" t="n">
-        <v>950.367828</v>
+        <v>910.047111</v>
       </c>
       <c r="I163" t="n">
-        <v>1083.211669</v>
+        <v>1057.075007</v>
       </c>
       <c r="J163" t="n">
         <v>1236.293463</v>
@@ -12838,19 +12838,19 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6747.014448</v>
+        <v>5551.722148</v>
       </c>
       <c r="F164" t="n">
-        <v>10560.246072</v>
+        <v>9100.383827</v>
       </c>
       <c r="G164" t="n">
-        <v>13296.562325</v>
+        <v>11884.397541</v>
       </c>
       <c r="H164" t="n">
-        <v>16303.78528</v>
+        <v>15061.325246</v>
       </c>
       <c r="I164" t="n">
-        <v>19653.027271</v>
+        <v>18817.533011</v>
       </c>
       <c r="J164" t="n">
         <v>23723.793584</v>
@@ -12914,19 +12914,19 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>4534.465181</v>
+        <v>4258.61604</v>
       </c>
       <c r="F165" t="n">
-        <v>6042.887705</v>
+        <v>5703.68213</v>
       </c>
       <c r="G165" t="n">
-        <v>7106.373043</v>
+        <v>6729.430682</v>
       </c>
       <c r="H165" t="n">
-        <v>8439.836751999999</v>
+        <v>8068.949897</v>
       </c>
       <c r="I165" t="n">
-        <v>9973.593462000001</v>
+        <v>9706.311054</v>
       </c>
       <c r="J165" t="n">
         <v>11824.711176</v>
@@ -12990,19 +12990,19 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>25620.834575</v>
+        <v>21750.860317</v>
       </c>
       <c r="F166" t="n">
-        <v>37784.984863</v>
+        <v>32999.229953</v>
       </c>
       <c r="G166" t="n">
-        <v>46436.399062</v>
+        <v>41699.939381</v>
       </c>
       <c r="H166" t="n">
-        <v>56067.902247</v>
+        <v>51828.925757</v>
       </c>
       <c r="I166" t="n">
-        <v>66758.75862199999</v>
+        <v>63877.388099</v>
       </c>
       <c r="J166" t="n">
         <v>79685.30893499999</v>
@@ -13066,19 +13066,19 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>66312.475613</v>
+        <v>72089.85679599999</v>
       </c>
       <c r="F167" t="n">
-        <v>60851.815073</v>
+        <v>67283.044245</v>
       </c>
       <c r="G167" t="n">
-        <v>57260.594385</v>
+        <v>63112.014163</v>
       </c>
       <c r="H167" t="n">
-        <v>56847.859789</v>
+        <v>61926.279824</v>
       </c>
       <c r="I167" t="n">
-        <v>55960.115729</v>
+        <v>59459.673102</v>
       </c>
       <c r="J167" t="n">
         <v>53106.616586</v>
@@ -13142,19 +13142,19 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1124.301622</v>
+        <v>1250.641987</v>
       </c>
       <c r="F168" t="n">
-        <v>1041.210932</v>
+        <v>1205.556113</v>
       </c>
       <c r="G168" t="n">
-        <v>953.282206</v>
+        <v>1123.845767</v>
       </c>
       <c r="H168" t="n">
-        <v>872.159451</v>
+        <v>1032.709696</v>
       </c>
       <c r="I168" t="n">
-        <v>731.253027</v>
+        <v>846.516922</v>
       </c>
       <c r="J168" t="n">
         <v>492.42804</v>
@@ -13218,19 +13218,19 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>57150.346922</v>
+        <v>51012.486695</v>
       </c>
       <c r="F169" t="n">
-        <v>83213.68620900001</v>
+        <v>75131.900504</v>
       </c>
       <c r="G169" t="n">
-        <v>104676.071998</v>
+        <v>96193.772377</v>
       </c>
       <c r="H169" t="n">
-        <v>130407.548323</v>
+        <v>122524.925147</v>
       </c>
       <c r="I169" t="n">
-        <v>159886.103268</v>
+        <v>154407.752852</v>
       </c>
       <c r="J169" t="n">
         <v>195445.413503</v>
@@ -13294,19 +13294,19 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>3783.438735</v>
+        <v>3271.923909</v>
       </c>
       <c r="F170" t="n">
-        <v>5853.985087</v>
+        <v>5222.71254</v>
       </c>
       <c r="G170" t="n">
-        <v>7496.326698</v>
+        <v>6870.411529</v>
       </c>
       <c r="H170" t="n">
-        <v>9398.844016999999</v>
+        <v>8824.575086999999</v>
       </c>
       <c r="I170" t="n">
-        <v>11603.658835</v>
+        <v>11197.049931</v>
       </c>
       <c r="J170" t="n">
         <v>14340.089702</v>
@@ -13370,19 +13370,19 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>20199.241394</v>
+        <v>19817.422332</v>
       </c>
       <c r="F171" t="n">
-        <v>23821.249552</v>
+        <v>23343.730799</v>
       </c>
       <c r="G171" t="n">
-        <v>26176.936475</v>
+        <v>25696.621487</v>
       </c>
       <c r="H171" t="n">
-        <v>29132.038096</v>
+        <v>28697.168664</v>
       </c>
       <c r="I171" t="n">
-        <v>32195.131173</v>
+        <v>31898.534768</v>
       </c>
       <c r="J171" t="n">
         <v>35660.216219</v>
@@ -13446,19 +13446,19 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>20424.670981</v>
+        <v>22786.931746</v>
       </c>
       <c r="F172" t="n">
-        <v>16822.975783</v>
+        <v>19490.615253</v>
       </c>
       <c r="G172" t="n">
-        <v>13570.007983</v>
+        <v>15853.129318</v>
       </c>
       <c r="H172" t="n">
-        <v>11420.262195</v>
+        <v>13192.730352</v>
       </c>
       <c r="I172" t="n">
-        <v>9591.550686</v>
+        <v>10680.546339</v>
       </c>
       <c r="J172" t="n">
         <v>7636.988516</v>
@@ -13522,19 +13522,19 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>267.24034</v>
+        <v>218.754148</v>
       </c>
       <c r="F173" t="n">
-        <v>440.437022</v>
+        <v>377.926947</v>
       </c>
       <c r="G173" t="n">
-        <v>582.807536</v>
+        <v>518.390608</v>
       </c>
       <c r="H173" t="n">
-        <v>753.4703950000001</v>
+        <v>692.781599</v>
       </c>
       <c r="I173" t="n">
-        <v>958.502494</v>
+        <v>914.9164489999999</v>
       </c>
       <c r="J173" t="n">
         <v>1218.542182</v>
@@ -13598,19 +13598,19 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>98880.568652</v>
+        <v>104049.005185</v>
       </c>
       <c r="F174" t="n">
-        <v>98266.264946</v>
+        <v>103957.636102</v>
       </c>
       <c r="G174" t="n">
-        <v>96924.533742</v>
+        <v>101950.964658</v>
       </c>
       <c r="H174" t="n">
-        <v>99443.94592899999</v>
+        <v>103638.486096</v>
       </c>
       <c r="I174" t="n">
-        <v>101708.494299</v>
+        <v>104496.507933</v>
       </c>
       <c r="J174" t="n">
         <v>102721.454651</v>
@@ -13674,19 +13674,19 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>688.2921669999999</v>
+        <v>598.19754</v>
       </c>
       <c r="F175" t="n">
-        <v>1079.928774</v>
+        <v>976.758055</v>
       </c>
       <c r="G175" t="n">
-        <v>1391.920405</v>
+        <v>1301.462216</v>
       </c>
       <c r="H175" t="n">
-        <v>1728.258035</v>
+        <v>1657.723203</v>
       </c>
       <c r="I175" t="n">
-        <v>2072.743195</v>
+        <v>2031.823842</v>
       </c>
       <c r="J175" t="n">
         <v>2435.487204</v>
@@ -13750,19 +13750,19 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>48.491139</v>
+        <v>41.878028</v>
       </c>
       <c r="F176" t="n">
-        <v>69.52211200000001</v>
+        <v>61.061511</v>
       </c>
       <c r="G176" t="n">
-        <v>84.613285</v>
+        <v>76.11702200000001</v>
       </c>
       <c r="H176" t="n">
-        <v>101.622862</v>
+        <v>93.98398299999999</v>
       </c>
       <c r="I176" t="n">
-        <v>120.417207</v>
+        <v>115.234076</v>
       </c>
       <c r="J176" t="n">
         <v>143.073946</v>
@@ -13826,19 +13826,19 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>80426.39519700001</v>
+        <v>79262.95974200001</v>
       </c>
       <c r="F177" t="n">
-        <v>104268.363787</v>
+        <v>105107.723038</v>
       </c>
       <c r="G177" t="n">
-        <v>118333.298418</v>
+        <v>121213.462951</v>
       </c>
       <c r="H177" t="n">
-        <v>129622.854767</v>
+        <v>133281.260574</v>
       </c>
       <c r="I177" t="n">
-        <v>136983.090346</v>
+        <v>139747.442048</v>
       </c>
       <c r="J177" t="n">
         <v>142769.141821</v>
@@ -13902,19 +13902,19 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>107.857131</v>
+        <v>89.01034</v>
       </c>
       <c r="F178" t="n">
-        <v>177.031228</v>
+        <v>152.187003</v>
       </c>
       <c r="G178" t="n">
-        <v>235.890209</v>
+        <v>209.655568</v>
       </c>
       <c r="H178" t="n">
-        <v>307.22045</v>
+        <v>282.110874</v>
       </c>
       <c r="I178" t="n">
-        <v>393.766466</v>
+        <v>375.512144</v>
       </c>
       <c r="J178" t="n">
         <v>504.548285</v>
@@ -13978,19 +13978,19 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>92.746325</v>
+        <v>82.190268</v>
       </c>
       <c r="F179" t="n">
-        <v>127.295517</v>
+        <v>114.362118</v>
       </c>
       <c r="G179" t="n">
-        <v>150.055314</v>
+        <v>137.611103</v>
       </c>
       <c r="H179" t="n">
-        <v>174.628891</v>
+        <v>163.787252</v>
       </c>
       <c r="I179" t="n">
-        <v>200.624313</v>
+        <v>193.425219</v>
       </c>
       <c r="J179" t="n">
         <v>230.796714</v>
@@ -14130,28 +14130,28 @@
         </is>
       </c>
       <c r="E181" t="n">
+        <v>-1e-06</v>
+      </c>
+      <c r="F181" t="n">
+        <v>-4e-06</v>
+      </c>
+      <c r="G181" t="n">
+        <v>-2e-06</v>
+      </c>
+      <c r="H181" t="n">
+        <v>-3e-06</v>
+      </c>
+      <c r="I181" t="n">
+        <v>-3e-06</v>
+      </c>
+      <c r="J181" t="n">
+        <v>2e-06</v>
+      </c>
+      <c r="K181" t="n">
+        <v>-5e-06</v>
+      </c>
+      <c r="L181" t="n">
         <v>0</v>
-      </c>
-      <c r="F181" t="n">
-        <v>-1e-06</v>
-      </c>
-      <c r="G181" t="n">
-        <v>-0</v>
-      </c>
-      <c r="H181" t="n">
-        <v>-5e-06</v>
-      </c>
-      <c r="I181" t="n">
-        <v>-1e-06</v>
-      </c>
-      <c r="J181" t="n">
-        <v>3e-06</v>
-      </c>
-      <c r="K181" t="n">
-        <v>-3e-06</v>
-      </c>
-      <c r="L181" t="n">
-        <v>2e-06</v>
       </c>
       <c r="M181" t="n">
         <v>-4e-06</v>
@@ -14160,28 +14160,28 @@
         <v>1e-06</v>
       </c>
       <c r="O181" t="n">
+        <v>1e-06</v>
+      </c>
+      <c r="P181" t="n">
+        <v>5e-06</v>
+      </c>
+      <c r="Q181" t="n">
+        <v>1e-06</v>
+      </c>
+      <c r="R181" t="n">
+        <v>-9e-06</v>
+      </c>
+      <c r="S181" t="n">
+        <v>-2e-06</v>
+      </c>
+      <c r="T181" t="n">
         <v>2e-06</v>
-      </c>
-      <c r="P181" t="n">
-        <v>4e-06</v>
-      </c>
-      <c r="Q181" t="n">
-        <v>0</v>
-      </c>
-      <c r="R181" t="n">
-        <v>-1e-05</v>
-      </c>
-      <c r="S181" t="n">
-        <v>-1e-06</v>
-      </c>
-      <c r="T181" t="n">
-        <v>3e-06</v>
       </c>
       <c r="U181" t="n">
         <v>1e-06</v>
       </c>
       <c r="V181" t="n">
-        <v>-5e-06</v>
+        <v>-4e-06</v>
       </c>
     </row>
   </sheetData>
